--- a/radseq_sample_sheet.xlsx
+++ b/radseq_sample_sheet.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RADseq\crystallinum\R_scripts\downstream_analysis\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671753C8-3959-49AC-B10A-34DFFD7550A1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24042" windowHeight="9491" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="full_details" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="excluded_samples" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Dean_plate1" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Dean_plate2" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="Admera_plate1" sheetId="5" r:id="rId8"/>
-    <sheet state="visible" name="Legend" sheetId="6" r:id="rId9"/>
+    <sheet name="full_details" sheetId="1" r:id="rId1"/>
+    <sheet name="excluded_samples" sheetId="2" r:id="rId2"/>
+    <sheet name="Dean_plate1" sheetId="3" r:id="rId3"/>
+    <sheet name="Dean_plate2" sheetId="4" r:id="rId4"/>
+    <sheet name="Admera_plate1" sheetId="5" r:id="rId5"/>
+    <sheet name="Legend" sheetId="6" r:id="rId6"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="/ZDXh2dvpCtQB9amCwhpUa0WCgVnf8P8GpjIaA6E/yA="/>
@@ -21,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1885" uniqueCount="368">
   <si>
     <t>Well (1st Batch_PlateA)</t>
   </si>
@@ -1005,31 +1014,152 @@
   </si>
   <si>
     <t xml:space="preserve">Uncertain, probably guerichianum </t>
+  </si>
+  <si>
+    <t>site</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>DWSA</t>
+  </si>
+  <si>
+    <t>PNSA</t>
+  </si>
+  <si>
+    <t>LBSA</t>
+  </si>
+  <si>
+    <t>BBSA</t>
+  </si>
+  <si>
+    <t>KBSA</t>
+  </si>
+  <si>
+    <t>WSSA</t>
+  </si>
+  <si>
+    <t>LPSA</t>
+  </si>
+  <si>
+    <t>SBSA</t>
+  </si>
+  <si>
+    <t>YZSA</t>
+  </si>
+  <si>
+    <t>HBSA</t>
+  </si>
+  <si>
+    <t>HKSA</t>
+  </si>
+  <si>
+    <t>AVSA</t>
+  </si>
+  <si>
+    <t>PBSA</t>
+  </si>
+  <si>
+    <t>GBSA</t>
+  </si>
+  <si>
+    <t>EBSA</t>
+  </si>
+  <si>
+    <t>GPSA</t>
+  </si>
+  <si>
+    <t>M2SA</t>
+  </si>
+  <si>
+    <t>MGSA</t>
+  </si>
+  <si>
+    <t>TBSA</t>
+  </si>
+  <si>
+    <t>MBSA</t>
+  </si>
+  <si>
+    <t>SSSA</t>
+  </si>
+  <si>
+    <t>EG</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>CI11</t>
+  </si>
+  <si>
+    <t>SA10</t>
+  </si>
+  <si>
+    <t>SA11</t>
+  </si>
+  <si>
+    <t>SA12</t>
+  </si>
+  <si>
+    <t>SA13</t>
+  </si>
+  <si>
+    <t>SA14</t>
+  </si>
+  <si>
+    <t>SA15</t>
+  </si>
+  <si>
+    <t>SA16</t>
+  </si>
+  <si>
+    <t>SA17</t>
+  </si>
+  <si>
+    <t>SA7</t>
+  </si>
+  <si>
+    <t>SA9</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>MEX</t>
+  </si>
+  <si>
+    <t>MOR</t>
+  </si>
+  <si>
+    <t>OUSA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
@@ -1039,7 +1169,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1049,70 +1179,49 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1302,28 +1411,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L1000"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.86"/>
-    <col customWidth="1" min="2" max="2" width="8.43"/>
-    <col customWidth="1" min="3" max="3" width="15.14"/>
-    <col customWidth="1" min="4" max="6" width="24.0"/>
-    <col customWidth="1" min="7" max="7" width="14.86"/>
-    <col customWidth="1" hidden="1" min="8" max="8" width="14.71"/>
-    <col customWidth="1" hidden="1" min="9" max="9" width="18.71"/>
-    <col customWidth="1" hidden="1" min="10" max="10" width="8.71"/>
-    <col customWidth="1" min="11" max="31" width="8.71"/>
+    <col min="1" max="1" width="8.88671875" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="18.6640625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" hidden="1" customWidth="1"/>
+    <col min="11" max="31" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1354,8 +1463,14 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" ht="14.25" customHeight="1">
+      <c r="K1" t="s">
+        <v>328</v>
+      </c>
+      <c r="L1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,16 +1489,19 @@
         <v>14</v>
       </c>
       <c r="H2" s="2">
-        <v>-32.703175</v>
+        <v>-32.703175000000002</v>
       </c>
       <c r="I2" s="2">
-        <v>18.2203036</v>
+        <v>18.220303600000001</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
+      <c r="K2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
@@ -1401,16 +1519,19 @@
         <v>17</v>
       </c>
       <c r="H3" s="2">
-        <v>-32.703175</v>
+        <v>-32.703175000000002</v>
       </c>
       <c r="I3" s="2">
-        <v>18.2203036</v>
+        <v>18.220303600000001</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
+      <c r="K3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -1429,16 +1550,19 @@
         <v>19</v>
       </c>
       <c r="H4" s="2">
-        <v>-32.703175</v>
+        <v>-32.703175000000002</v>
       </c>
       <c r="I4" s="2">
-        <v>18.2203036</v>
+        <v>18.220303600000001</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
+      <c r="K4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
@@ -1457,16 +1581,19 @@
         <v>21</v>
       </c>
       <c r="H5" s="2">
-        <v>-32.703175</v>
+        <v>-32.703175000000002</v>
       </c>
       <c r="I5" s="2">
-        <v>18.2203036</v>
+        <v>18.220303600000001</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
+      <c r="K5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
@@ -1485,7 +1612,7 @@
         <v>24</v>
       </c>
       <c r="H6" s="2">
-        <v>-32.8095899</v>
+        <v>-32.809589899999999</v>
       </c>
       <c r="I6" s="2">
         <v>17.8910406</v>
@@ -1493,8 +1620,11 @@
       <c r="J6" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
+      <c r="K6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
@@ -1513,7 +1643,7 @@
         <v>26</v>
       </c>
       <c r="H7" s="2">
-        <v>-32.8095899</v>
+        <v>-32.809589899999999</v>
       </c>
       <c r="I7" s="2">
         <v>17.8910406</v>
@@ -1521,8 +1651,11 @@
       <c r="J7" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
+      <c r="K7" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
@@ -1541,7 +1674,7 @@
         <v>28</v>
       </c>
       <c r="H8" s="2">
-        <v>-32.8095899</v>
+        <v>-32.809589899999999</v>
       </c>
       <c r="I8" s="2">
         <v>17.8910406</v>
@@ -1549,8 +1682,11 @@
       <c r="J8" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
+      <c r="K8" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
@@ -1569,16 +1705,19 @@
         <v>31</v>
       </c>
       <c r="H9" s="2">
-        <v>-33.0973151</v>
+        <v>-33.097315100000003</v>
       </c>
       <c r="I9" s="2">
-        <v>18.0303847</v>
+        <v>18.030384699999999</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
+      <c r="K9" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
@@ -1597,16 +1736,19 @@
         <v>33</v>
       </c>
       <c r="H10" s="2">
-        <v>-33.0973151</v>
+        <v>-33.097315100000003</v>
       </c>
       <c r="I10" s="2">
-        <v>18.0303847</v>
+        <v>18.030384699999999</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
+      <c r="K10" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
@@ -1625,16 +1767,19 @@
         <v>35</v>
       </c>
       <c r="H11" s="2">
-        <v>-33.0973151</v>
+        <v>-33.097315100000003</v>
       </c>
       <c r="I11" s="2">
-        <v>18.0303847</v>
+        <v>18.030384699999999</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
+      <c r="K11" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
@@ -1653,16 +1798,19 @@
         <v>38</v>
       </c>
       <c r="H12" s="2">
-        <v>-33.8158702</v>
+        <v>-33.815870199999999</v>
       </c>
       <c r="I12" s="2">
-        <v>18.4728083</v>
+        <v>18.472808300000001</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
+      <c r="K12" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
@@ -1681,16 +1829,19 @@
         <v>40</v>
       </c>
       <c r="H13" s="2">
-        <v>-33.8158702</v>
+        <v>-33.815870199999999</v>
       </c>
       <c r="I13" s="2">
-        <v>18.4728083</v>
+        <v>18.472808300000001</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
+      <c r="K13" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
@@ -1709,16 +1860,19 @@
         <v>42</v>
       </c>
       <c r="H14" s="2">
-        <v>-33.8158702</v>
+        <v>-33.815870199999999</v>
       </c>
       <c r="I14" s="2">
-        <v>18.4728083</v>
+        <v>18.472808300000001</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
+      <c r="K14" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
@@ -1737,16 +1891,19 @@
         <v>44</v>
       </c>
       <c r="H15" s="2">
-        <v>-34.1302817</v>
+        <v>-34.130281699999998</v>
       </c>
       <c r="I15" s="2">
-        <v>18.4490876</v>
+        <v>18.449087599999999</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
+      <c r="K15" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
@@ -1765,16 +1922,19 @@
         <v>46</v>
       </c>
       <c r="H16" s="2">
-        <v>-34.1302817</v>
+        <v>-34.130281699999998</v>
       </c>
       <c r="I16" s="2">
-        <v>18.4490876</v>
+        <v>18.449087599999999</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
+      <c r="K16" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
@@ -1793,16 +1953,19 @@
         <v>48</v>
       </c>
       <c r="H17" s="2">
-        <v>-34.1302817</v>
+        <v>-34.130281699999998</v>
       </c>
       <c r="I17" s="2">
-        <v>18.4490876</v>
+        <v>18.449087599999999</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
+      <c r="K17" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
@@ -1821,16 +1984,19 @@
         <v>51</v>
       </c>
       <c r="H18" s="2">
-        <v>-34.39463</v>
+        <v>-34.394629999999999</v>
       </c>
       <c r="I18" s="2">
-        <v>20.8469878</v>
+        <v>20.846987800000001</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" ht="14.25" customHeight="1">
+      <c r="K18" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
@@ -1849,16 +2015,19 @@
         <v>52</v>
       </c>
       <c r="H19" s="2">
-        <v>-34.39463</v>
+        <v>-34.394629999999999</v>
       </c>
       <c r="I19" s="2">
-        <v>20.8469878</v>
+        <v>20.846987800000001</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
+      <c r="K19" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
@@ -1877,16 +2046,19 @@
         <v>54</v>
       </c>
       <c r="H20" s="2">
-        <v>-34.39463</v>
+        <v>-34.394629999999999</v>
       </c>
       <c r="I20" s="2">
-        <v>20.8469878</v>
+        <v>20.846987800000001</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
+      <c r="K20" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
@@ -1905,7 +2077,7 @@
         <v>57</v>
       </c>
       <c r="H21" s="2">
-        <v>-32.2199328</v>
+        <v>-32.219932800000002</v>
       </c>
       <c r="I21" s="2">
         <v>18.4802766</v>
@@ -1913,8 +2085,11 @@
       <c r="J21" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
+      <c r="K21" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
@@ -1933,7 +2108,7 @@
         <v>59</v>
       </c>
       <c r="H22" s="2">
-        <v>-32.2199328</v>
+        <v>-32.219932800000002</v>
       </c>
       <c r="I22" s="2">
         <v>18.4802766</v>
@@ -1941,8 +2116,11 @@
       <c r="J22" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" ht="14.25" customHeight="1">
+      <c r="K22" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
@@ -1961,7 +2139,7 @@
         <v>61</v>
       </c>
       <c r="H23" s="2">
-        <v>-32.2199328</v>
+        <v>-32.219932800000002</v>
       </c>
       <c r="I23" s="2">
         <v>18.4802766</v>
@@ -1969,8 +2147,11 @@
       <c r="J23" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" ht="14.25" customHeight="1">
+      <c r="K23" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
@@ -1992,13 +2173,16 @@
         <v>-34.831944</v>
       </c>
       <c r="I24" s="2">
-        <v>20.001667</v>
+        <v>20.001667000000001</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" ht="14.25" customHeight="1">
+      <c r="K24" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
@@ -2020,13 +2204,16 @@
         <v>-34.831944</v>
       </c>
       <c r="I25" s="2">
-        <v>20.001667</v>
+        <v>20.001667000000001</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="26" ht="14.25" customHeight="1">
+      <c r="K25" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
@@ -2048,13 +2235,16 @@
         <v>-34.831944</v>
       </c>
       <c r="I26" s="2">
-        <v>20.001667</v>
+        <v>20.001667000000001</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="27" ht="14.25" customHeight="1">
+      <c r="K26" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
@@ -2073,16 +2263,19 @@
         <v>71</v>
       </c>
       <c r="H27" s="2">
-        <v>-33.3447647</v>
+        <v>-33.344764699999999</v>
       </c>
       <c r="I27" s="2">
-        <v>18.1623146</v>
+        <v>18.162314599999998</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="28" ht="14.25" customHeight="1">
+      <c r="K27" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
@@ -2101,16 +2294,19 @@
         <v>73</v>
       </c>
       <c r="H28" s="2">
-        <v>-33.3447647</v>
+        <v>-33.344764699999999</v>
       </c>
       <c r="I28" s="2">
-        <v>18.1623146</v>
+        <v>18.162314599999998</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" ht="14.25" customHeight="1">
+      <c r="K28" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
@@ -2129,16 +2325,19 @@
         <v>75</v>
       </c>
       <c r="H29" s="2">
-        <v>-33.3447647</v>
+        <v>-33.344764699999999</v>
       </c>
       <c r="I29" s="2">
-        <v>18.1623146</v>
+        <v>18.162314599999998</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="30" ht="14.25" customHeight="1">
+      <c r="K29" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
@@ -2160,13 +2359,16 @@
         <v>-34.402428</v>
       </c>
       <c r="I30" s="2">
-        <v>19.123211</v>
+        <v>19.123211000000001</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="31" ht="14.25" customHeight="1">
+      <c r="K30" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
@@ -2188,13 +2390,16 @@
         <v>-34.402428</v>
       </c>
       <c r="I31" s="2">
-        <v>19.123211</v>
+        <v>19.123211000000001</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="32" ht="14.25" customHeight="1">
+      <c r="K31" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
@@ -2216,13 +2421,16 @@
         <v>-34.402428</v>
       </c>
       <c r="I32" s="2">
-        <v>19.123211</v>
+        <v>19.123211000000001</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" ht="14.25" customHeight="1">
+      <c r="K32" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
@@ -2241,16 +2449,19 @@
         <v>85</v>
       </c>
       <c r="H33" s="2">
-        <v>-30.314914</v>
+        <v>-30.314914000000002</v>
       </c>
       <c r="I33" s="2">
-        <v>17.275844</v>
+        <v>17.275843999999999</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="34" ht="14.25" customHeight="1">
+      <c r="K33" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1" t="s">
@@ -2269,16 +2480,19 @@
         <v>87</v>
       </c>
       <c r="H34" s="2">
-        <v>-30.314914</v>
+        <v>-30.314914000000002</v>
       </c>
       <c r="I34" s="2">
-        <v>17.275844</v>
+        <v>17.275843999999999</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="35" ht="14.25" customHeight="1">
+      <c r="K34" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
@@ -2297,16 +2511,19 @@
         <v>89</v>
       </c>
       <c r="H35" s="2">
-        <v>-30.314914</v>
+        <v>-30.314914000000002</v>
       </c>
       <c r="I35" s="2">
-        <v>17.275844</v>
+        <v>17.275843999999999</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="36" ht="14.25" customHeight="1">
+      <c r="K35" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
@@ -2325,7 +2542,7 @@
         <v>92</v>
       </c>
       <c r="H36" s="2">
-        <v>-34.665278</v>
+        <v>-34.665278000000001</v>
       </c>
       <c r="I36" s="2">
         <v>20.232222</v>
@@ -2333,8 +2550,11 @@
       <c r="J36" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="37" ht="14.25" customHeight="1">
+      <c r="K36" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
@@ -2353,7 +2573,7 @@
         <v>94</v>
       </c>
       <c r="H37" s="2">
-        <v>-34.665278</v>
+        <v>-34.665278000000001</v>
       </c>
       <c r="I37" s="2">
         <v>20.232222</v>
@@ -2361,8 +2581,11 @@
       <c r="J37" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="38" ht="14.25" customHeight="1">
+      <c r="K37" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
@@ -2381,7 +2604,7 @@
         <v>96</v>
       </c>
       <c r="H38" s="2">
-        <v>-34.665278</v>
+        <v>-34.665278000000001</v>
       </c>
       <c r="I38" s="2">
         <v>20.232222</v>
@@ -2389,8 +2612,11 @@
       <c r="J38" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="39" ht="14.25" customHeight="1">
+      <c r="K38" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1" t="s">
@@ -2409,7 +2635,7 @@
         <v>99</v>
       </c>
       <c r="H39" s="2">
-        <v>-34.3966518</v>
+        <v>-34.396651800000001</v>
       </c>
       <c r="I39" s="2">
         <v>20.8253162</v>
@@ -2417,8 +2643,11 @@
       <c r="J39" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="40" ht="14.25" customHeight="1">
+      <c r="K39" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
@@ -2437,7 +2666,7 @@
         <v>101</v>
       </c>
       <c r="H40" s="2">
-        <v>-34.3966518</v>
+        <v>-34.396651800000001</v>
       </c>
       <c r="I40" s="2">
         <v>20.8253162</v>
@@ -2445,8 +2674,11 @@
       <c r="J40" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="41" ht="14.25" customHeight="1">
+      <c r="K40" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
@@ -2465,7 +2697,7 @@
         <v>103</v>
       </c>
       <c r="H41" s="2">
-        <v>-34.3966518</v>
+        <v>-34.396651800000001</v>
       </c>
       <c r="I41" s="2">
         <v>20.8253162</v>
@@ -2473,8 +2705,11 @@
       <c r="J41" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="42" ht="14.25" customHeight="1">
+      <c r="K41" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
@@ -2493,16 +2728,19 @@
         <v>106</v>
       </c>
       <c r="H42" s="2">
-        <v>-34.624917</v>
+        <v>-34.624917000000003</v>
       </c>
       <c r="I42" s="2">
-        <v>19.336563</v>
+        <v>19.336563000000002</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="43" ht="14.25" customHeight="1">
+      <c r="K42" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
@@ -2521,16 +2759,19 @@
         <v>108</v>
       </c>
       <c r="H43" s="2">
-        <v>-34.624917</v>
+        <v>-34.624917000000003</v>
       </c>
       <c r="I43" s="2">
-        <v>19.336563</v>
+        <v>19.336563000000002</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="44" ht="14.25" customHeight="1">
+      <c r="K43" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
@@ -2549,16 +2790,19 @@
         <v>110</v>
       </c>
       <c r="H44" s="2">
-        <v>-34.624917</v>
+        <v>-34.624917000000003</v>
       </c>
       <c r="I44" s="2">
-        <v>19.336563</v>
+        <v>19.336563000000002</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="45" ht="14.25" customHeight="1">
+      <c r="K44" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
@@ -2577,16 +2821,19 @@
         <v>112</v>
       </c>
       <c r="H45" s="2">
-        <v>-32.340981</v>
+        <v>-32.340980999999999</v>
       </c>
       <c r="I45" s="2">
-        <v>18.319755</v>
+        <v>18.319755000000001</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="46" ht="14.25" customHeight="1">
+      <c r="K45" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
@@ -2605,16 +2852,19 @@
         <v>114</v>
       </c>
       <c r="H46" s="2">
-        <v>-32.340981</v>
+        <v>-32.340980999999999</v>
       </c>
       <c r="I46" s="2">
-        <v>18.319755</v>
+        <v>18.319755000000001</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="47" ht="14.25" customHeight="1">
+      <c r="K46" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1" t="s">
@@ -2633,16 +2883,19 @@
         <v>116</v>
       </c>
       <c r="H47" s="2">
-        <v>-32.340981</v>
+        <v>-32.340980999999999</v>
       </c>
       <c r="I47" s="2">
-        <v>18.319755</v>
+        <v>18.319755000000001</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="48" ht="14.25" customHeight="1">
+      <c r="K47" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1" t="s">
@@ -2661,16 +2914,19 @@
         <v>118</v>
       </c>
       <c r="H48" s="2">
-        <v>-33.904219</v>
+        <v>-33.904218999999998</v>
       </c>
       <c r="I48" s="2">
-        <v>18.397974</v>
+        <v>18.397974000000001</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="49" ht="14.25" customHeight="1">
+      <c r="K48" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1" t="s">
@@ -2689,16 +2945,19 @@
         <v>120</v>
       </c>
       <c r="H49" s="2">
-        <v>-33.904219</v>
+        <v>-33.904218999999998</v>
       </c>
       <c r="I49" s="2">
-        <v>18.397974</v>
+        <v>18.397974000000001</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="50" ht="14.25" customHeight="1">
+      <c r="K49" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
@@ -2717,16 +2976,19 @@
         <v>122</v>
       </c>
       <c r="H50" s="2">
-        <v>-33.904219</v>
+        <v>-33.904218999999998</v>
       </c>
       <c r="I50" s="2">
-        <v>18.397974</v>
+        <v>18.397974000000001</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="51" ht="14.25" customHeight="1">
+      <c r="K50" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1" t="s">
@@ -2745,16 +3007,19 @@
         <v>125</v>
       </c>
       <c r="H51" s="2">
-        <v>-33.720556</v>
+        <v>-33.720556000000002</v>
       </c>
       <c r="I51" s="2">
-        <v>18.451389</v>
+        <v>18.451388999999999</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="52" ht="14.25" customHeight="1">
+      <c r="K51" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1" t="s">
@@ -2773,16 +3038,19 @@
         <v>127</v>
       </c>
       <c r="H52" s="2">
-        <v>-33.720556</v>
+        <v>-33.720556000000002</v>
       </c>
       <c r="I52" s="2">
-        <v>18.451389</v>
+        <v>18.451388999999999</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="53" ht="14.25" customHeight="1">
+      <c r="K52" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1" t="s">
@@ -2801,16 +3069,19 @@
         <v>129</v>
       </c>
       <c r="H53" s="2">
-        <v>-33.720556</v>
+        <v>-33.720556000000002</v>
       </c>
       <c r="I53" s="2">
-        <v>18.451389</v>
+        <v>18.451388999999999</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="54" ht="14.25" customHeight="1">
+      <c r="K53" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
@@ -2829,16 +3100,19 @@
         <v>132</v>
       </c>
       <c r="H54" s="2">
-        <v>-34.302167</v>
+        <v>-34.302166999999997</v>
       </c>
       <c r="I54" s="2">
-        <v>20.591117</v>
+        <v>20.591117000000001</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="55" ht="14.25" customHeight="1">
+      <c r="K54" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1" t="s">
@@ -2857,16 +3131,19 @@
         <v>134</v>
       </c>
       <c r="H55" s="2">
-        <v>-34.302167</v>
+        <v>-34.302166999999997</v>
       </c>
       <c r="I55" s="2">
-        <v>20.591117</v>
+        <v>20.591117000000001</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="56" ht="14.25" customHeight="1">
+      <c r="K55" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1" t="s">
@@ -2885,16 +3162,19 @@
         <v>136</v>
       </c>
       <c r="H56" s="2">
-        <v>-34.302167</v>
+        <v>-34.302166999999997</v>
       </c>
       <c r="I56" s="2">
-        <v>20.591117</v>
+        <v>20.591117000000001</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="57" ht="14.25" customHeight="1">
+      <c r="K56" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1" t="s">
@@ -2913,16 +3193,19 @@
         <v>139</v>
       </c>
       <c r="H57" s="2">
-        <v>-33.85833</v>
+        <v>-33.858330000000002</v>
       </c>
       <c r="I57" s="2">
-        <v>18.489444</v>
+        <v>18.489443999999999</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="58" ht="14.25" customHeight="1">
+      <c r="K57" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1" t="s">
@@ -2941,16 +3224,19 @@
         <v>141</v>
       </c>
       <c r="H58" s="2">
-        <v>-33.85833</v>
+        <v>-33.858330000000002</v>
       </c>
       <c r="I58" s="2">
-        <v>18.489444</v>
+        <v>18.489443999999999</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="59" ht="14.25" customHeight="1">
+      <c r="K58" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1" t="s">
@@ -2969,16 +3255,19 @@
         <v>142</v>
       </c>
       <c r="H59" s="2">
-        <v>-33.85833</v>
+        <v>-33.858330000000002</v>
       </c>
       <c r="I59" s="2">
-        <v>18.489444</v>
+        <v>18.489443999999999</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="60" ht="14.25" customHeight="1">
+      <c r="K59" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1" t="s">
@@ -2997,16 +3286,19 @@
         <v>145</v>
       </c>
       <c r="H60" s="2">
-        <v>-33.7243466</v>
+        <v>-33.724346599999997</v>
       </c>
       <c r="I60" s="2">
-        <v>18.4429942</v>
+        <v>18.442994200000001</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="61" ht="14.25" customHeight="1">
+      <c r="K60" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1" t="s">
@@ -3025,16 +3317,19 @@
         <v>147</v>
       </c>
       <c r="H61" s="2">
-        <v>-33.7243466</v>
+        <v>-33.724346599999997</v>
       </c>
       <c r="I61" s="2">
-        <v>18.4429942</v>
+        <v>18.442994200000001</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="62" ht="14.25" customHeight="1">
+      <c r="K61" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4" t="s">
@@ -3053,16 +3348,19 @@
         <v>149</v>
       </c>
       <c r="H62" s="5">
-        <v>-33.7243466</v>
+        <v>-33.724346599999997</v>
       </c>
       <c r="I62" s="5">
-        <v>18.4429942</v>
+        <v>18.442994200000001</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="63" ht="14.25" customHeight="1">
+      <c r="K62" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1" t="s">
@@ -3081,16 +3379,19 @@
         <v>152</v>
       </c>
       <c r="H63" s="2">
-        <v>-33.5909892</v>
+        <v>-33.590989200000003</v>
       </c>
       <c r="I63" s="2">
-        <v>18.3621042</v>
+        <v>18.362104200000001</v>
       </c>
       <c r="J63" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="64" ht="14.25" customHeight="1">
+      <c r="K63" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1" t="s">
@@ -3109,16 +3410,19 @@
         <v>154</v>
       </c>
       <c r="H64" s="2">
-        <v>-33.5909892</v>
+        <v>-33.590989200000003</v>
       </c>
       <c r="I64" s="2">
-        <v>18.3621042</v>
+        <v>18.362104200000001</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="65" ht="14.25" customHeight="1">
+      <c r="K64" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
@@ -3137,16 +3441,19 @@
         <v>155</v>
       </c>
       <c r="H65" s="2">
-        <v>-33.5909892</v>
+        <v>-33.590989200000003</v>
       </c>
       <c r="I65" s="2">
-        <v>18.3621042</v>
+        <v>18.362104200000001</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="66" ht="14.25" customHeight="1">
+      <c r="K65" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>107</v>
       </c>
@@ -3173,8 +3480,11 @@
       <c r="J66" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="67" ht="14.25" customHeight="1">
+      <c r="K66" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2"/>
       <c r="B67" s="1" t="s">
         <v>93</v>
@@ -3193,16 +3503,19 @@
         <v>160</v>
       </c>
       <c r="H67" s="2">
-        <v>35.1264</v>
+        <v>35.126399999999997</v>
       </c>
       <c r="I67" s="2">
-        <v>33.4299</v>
+        <v>33.429900000000004</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="68" ht="14.25" customHeight="1">
+      <c r="K67" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>34</v>
       </c>
@@ -3221,16 +3534,19 @@
         <v>161</v>
       </c>
       <c r="H68" s="2">
-        <v>35.1264</v>
+        <v>35.126399999999997</v>
       </c>
       <c r="I68" s="2">
-        <v>33.4299</v>
+        <v>33.429900000000004</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="69" ht="14.25" customHeight="1">
+      <c r="K68" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>162</v>
       </c>
@@ -3249,16 +3565,19 @@
         <v>163</v>
       </c>
       <c r="H69" s="2">
-        <v>35.1264</v>
+        <v>35.126399999999997</v>
       </c>
       <c r="I69" s="2">
-        <v>33.4299</v>
+        <v>33.429900000000004</v>
       </c>
       <c r="J69" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="70" ht="14.25" customHeight="1">
+      <c r="K69" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2"/>
       <c r="B70" s="1" t="s">
         <v>164</v>
@@ -3277,16 +3596,19 @@
         <v>165</v>
       </c>
       <c r="H70" s="2">
-        <v>35.1264</v>
+        <v>35.126399999999997</v>
       </c>
       <c r="I70" s="2">
-        <v>33.4299</v>
+        <v>33.429900000000004</v>
       </c>
       <c r="J70" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="71" ht="14.25" customHeight="1">
+      <c r="K70" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>97</v>
       </c>
@@ -3305,7 +3627,7 @@
         <v>167</v>
       </c>
       <c r="H71" s="2">
-        <v>31.356111</v>
+        <v>31.356110999999999</v>
       </c>
       <c r="I71" s="2">
         <v>27.2075</v>
@@ -3313,8 +3635,11 @@
       <c r="J71" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="72" ht="14.25" customHeight="1">
+      <c r="K71" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>133</v>
       </c>
@@ -3333,7 +3658,7 @@
         <v>168</v>
       </c>
       <c r="H72" s="2">
-        <v>31.2675</v>
+        <v>31.267499999999998</v>
       </c>
       <c r="I72" s="2">
         <v>30.178611</v>
@@ -3341,8 +3666,11 @@
       <c r="J72" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="73" ht="14.25" customHeight="1">
+      <c r="K72" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>45</v>
       </c>
@@ -3361,7 +3689,7 @@
         <v>169</v>
       </c>
       <c r="H73" s="2">
-        <v>31.2675</v>
+        <v>31.267499999999998</v>
       </c>
       <c r="I73" s="2">
         <v>30.178611</v>
@@ -3369,8 +3697,11 @@
       <c r="J73" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="74" ht="14.25" customHeight="1">
+      <c r="K73" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>60</v>
       </c>
@@ -3389,7 +3720,7 @@
         <v>170</v>
       </c>
       <c r="H74" s="2">
-        <v>31.356111</v>
+        <v>31.356110999999999</v>
       </c>
       <c r="I74" s="2">
         <v>27.2075</v>
@@ -3397,8 +3728,11 @@
       <c r="J74" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="75" ht="14.25" customHeight="1">
+      <c r="K74" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>171</v>
       </c>
@@ -3417,7 +3751,7 @@
         <v>172</v>
       </c>
       <c r="H75" s="2">
-        <v>31.356111</v>
+        <v>31.356110999999999</v>
       </c>
       <c r="I75" s="2">
         <v>27.2075</v>
@@ -3425,8 +3759,11 @@
       <c r="J75" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="76" ht="14.25" customHeight="1">
+      <c r="K75" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>69</v>
       </c>
@@ -3445,7 +3782,7 @@
         <v>173</v>
       </c>
       <c r="H76" s="2">
-        <v>31.2675</v>
+        <v>31.267499999999998</v>
       </c>
       <c r="I76" s="2">
         <v>30.178611</v>
@@ -3453,8 +3790,11 @@
       <c r="J76" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="77" ht="14.25" customHeight="1">
+      <c r="K76" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>100</v>
       </c>
@@ -3473,7 +3813,7 @@
         <v>174</v>
       </c>
       <c r="H77" s="2">
-        <v>31.2675</v>
+        <v>31.267499999999998</v>
       </c>
       <c r="I77" s="2">
         <v>30.178611</v>
@@ -3481,8 +3821,11 @@
       <c r="J77" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="78" ht="14.25" customHeight="1">
+      <c r="K77" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>130</v>
       </c>
@@ -3501,16 +3844,19 @@
         <v>176</v>
       </c>
       <c r="H78" s="2">
-        <v>37.976667</v>
+        <v>37.976666999999999</v>
       </c>
       <c r="I78" s="2">
-        <v>12.495556</v>
+        <v>12.495556000000001</v>
       </c>
       <c r="J78" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="79" ht="14.25" customHeight="1">
+      <c r="K78" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>177</v>
       </c>
@@ -3529,16 +3875,19 @@
         <v>178</v>
       </c>
       <c r="H79" s="2">
-        <v>37.976667</v>
+        <v>37.976666999999999</v>
       </c>
       <c r="I79" s="2">
-        <v>12.495556</v>
+        <v>12.495556000000001</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="80" ht="14.25" customHeight="1">
+      <c r="K79" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>179</v>
       </c>
@@ -3557,16 +3906,19 @@
         <v>180</v>
       </c>
       <c r="H80" s="2">
-        <v>37.976667</v>
+        <v>37.976666999999999</v>
       </c>
       <c r="I80" s="2">
-        <v>12.495556</v>
+        <v>12.495556000000001</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="81" ht="14.25" customHeight="1">
+      <c r="K80" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>36</v>
       </c>
@@ -3585,16 +3937,19 @@
         <v>181</v>
       </c>
       <c r="H81" s="2">
-        <v>37.976667</v>
+        <v>37.976666999999999</v>
       </c>
       <c r="I81" s="2">
-        <v>12.495556</v>
+        <v>12.495556000000001</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="82" ht="14.25" customHeight="1">
+      <c r="K81" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>55</v>
       </c>
@@ -3613,16 +3968,19 @@
         <v>182</v>
       </c>
       <c r="H82" s="2">
-        <v>35.501667</v>
+        <v>35.501666999999998</v>
       </c>
       <c r="I82" s="2">
-        <v>12.602778</v>
+        <v>12.602778000000001</v>
       </c>
       <c r="J82" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="83" ht="14.25" customHeight="1">
+      <c r="K82" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>95</v>
       </c>
@@ -3649,8 +4007,11 @@
       <c r="J83" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="84" ht="14.25" customHeight="1">
+      <c r="K83" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2"/>
       <c r="B84" s="1" t="s">
         <v>140</v>
@@ -3669,7 +4030,7 @@
         <v>186</v>
       </c>
       <c r="H84" s="2">
-        <v>27.493639</v>
+        <v>27.493639000000002</v>
       </c>
       <c r="I84" s="2">
         <v>-114.14928</v>
@@ -3677,8 +4038,11 @@
       <c r="J84" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="85" ht="14.25" customHeight="1">
+      <c r="K84" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2"/>
       <c r="B85" s="1" t="s">
         <v>25</v>
@@ -3697,7 +4061,7 @@
         <v>187</v>
       </c>
       <c r="H85" s="2">
-        <v>27.455167</v>
+        <v>27.455166999999999</v>
       </c>
       <c r="I85" s="2">
         <v>-114.135575</v>
@@ -3705,8 +4069,11 @@
       <c r="J85" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="86" ht="14.25" customHeight="1">
+      <c r="K85" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>126</v>
       </c>
@@ -3733,8 +4100,11 @@
       <c r="J86" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="87" ht="14.25" customHeight="1">
+      <c r="K86" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>189</v>
       </c>
@@ -3753,7 +4123,7 @@
         <v>190</v>
       </c>
       <c r="H87" s="2">
-        <v>30.48589392</v>
+        <v>30.485893919999999</v>
       </c>
       <c r="I87" s="2">
         <v>-116.1046225</v>
@@ -3761,8 +4131,11 @@
       <c r="J87" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="88" ht="14.25" customHeight="1">
+      <c r="K87" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2"/>
       <c r="B88" s="1" t="s">
         <v>62</v>
@@ -3781,16 +4154,19 @@
         <v>192</v>
       </c>
       <c r="H88" s="2">
-        <v>28.823333</v>
+        <v>28.823333000000002</v>
       </c>
       <c r="I88" s="2">
-        <v>-10.287778</v>
+        <v>-10.287777999999999</v>
       </c>
       <c r="J88" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="89" ht="14.25" customHeight="1">
+      <c r="K88" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2"/>
       <c r="B89" s="1" t="s">
         <v>81</v>
@@ -3809,16 +4185,19 @@
         <v>193</v>
       </c>
       <c r="H89" s="2">
-        <v>28.823333</v>
+        <v>28.823333000000002</v>
       </c>
       <c r="I89" s="2">
-        <v>-10.287778</v>
+        <v>-10.287777999999999</v>
       </c>
       <c r="J89" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="90" ht="14.25" customHeight="1">
+      <c r="K89" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2"/>
       <c r="B90" s="1" t="s">
         <v>194</v>
@@ -3845,8 +4224,11 @@
       <c r="J90" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="91" ht="14.25" customHeight="1">
+      <c r="K90" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2"/>
       <c r="B91" s="1" t="s">
         <v>198</v>
@@ -3873,8 +4255,11 @@
       <c r="J91" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="92" ht="14.25" customHeight="1">
+      <c r="K91" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>140</v>
       </c>
@@ -3893,7 +4278,7 @@
         <v>200</v>
       </c>
       <c r="H92" s="2">
-        <v>32.41229</v>
+        <v>32.412289999999999</v>
       </c>
       <c r="I92" s="2">
         <v>-117.245304</v>
@@ -3901,8 +4286,11 @@
       <c r="J92" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="93" ht="14.25" customHeight="1">
+      <c r="K92" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>201</v>
       </c>
@@ -3921,7 +4309,7 @@
         <v>202</v>
       </c>
       <c r="H93" s="2">
-        <v>32.40162</v>
+        <v>32.401620000000001</v>
       </c>
       <c r="I93" s="2">
         <v>-117.24294</v>
@@ -3929,8 +4317,11 @@
       <c r="J93" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="94" ht="14.25" customHeight="1">
+      <c r="K93" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>135</v>
       </c>
@@ -3949,7 +4340,7 @@
         <v>203</v>
       </c>
       <c r="H94" s="2">
-        <v>34.38721</v>
+        <v>34.387210000000003</v>
       </c>
       <c r="I94" s="2">
         <v>-119.51183</v>
@@ -3957,8 +4348,11 @@
       <c r="J94" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="95" ht="14.25" customHeight="1">
+      <c r="K94" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>119</v>
       </c>
@@ -3985,8 +4379,11 @@
       <c r="J95" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="96" ht="14.25" customHeight="1">
+      <c r="K95" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>205</v>
       </c>
@@ -4005,7 +4402,7 @@
         <v>206</v>
       </c>
       <c r="H96" s="2">
-        <v>34.38707</v>
+        <v>34.387070000000001</v>
       </c>
       <c r="I96" s="2">
         <v>-119.51093</v>
@@ -4013,8 +4410,11 @@
       <c r="J96" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="97" ht="14.25" customHeight="1">
+      <c r="K96" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>207</v>
       </c>
@@ -4033,7 +4433,7 @@
         <v>208</v>
       </c>
       <c r="H97" s="2">
-        <v>36.51207</v>
+        <v>36.512070000000001</v>
       </c>
       <c r="I97" s="2">
         <v>-121.94215</v>
@@ -4041,8 +4441,11 @@
       <c r="J97" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="98" ht="14.25" customHeight="1">
+      <c r="K97" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>115</v>
       </c>
@@ -4061,7 +4464,7 @@
         <v>209</v>
       </c>
       <c r="H98" s="2">
-        <v>34.38737</v>
+        <v>34.387369999999997</v>
       </c>
       <c r="I98" s="2">
         <v>-119.51226</v>
@@ -4069,8 +4472,11 @@
       <c r="J98" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="99" ht="14.25" customHeight="1">
+      <c r="K98" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>58</v>
       </c>
@@ -4089,7 +4495,7 @@
         <v>210</v>
       </c>
       <c r="H99" s="2">
-        <v>34.01528</v>
+        <v>34.015279999999997</v>
       </c>
       <c r="I99" s="2">
         <v>-119.36194</v>
@@ -4097,8 +4503,11 @@
       <c r="J99" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="100" ht="14.25" customHeight="1">
+      <c r="K99" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>41</v>
       </c>
@@ -4117,7 +4526,7 @@
         <v>211</v>
       </c>
       <c r="H100" s="2">
-        <v>34.01583</v>
+        <v>34.015830000000001</v>
       </c>
       <c r="I100" s="2">
         <v>-119.36028</v>
@@ -4125,8 +4534,11 @@
       <c r="J100" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="101" ht="14.25" customHeight="1">
+      <c r="K100" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>212</v>
       </c>
@@ -4145,7 +4557,7 @@
         <v>213</v>
       </c>
       <c r="H101" s="2">
-        <v>34.01528</v>
+        <v>34.015279999999997</v>
       </c>
       <c r="I101" s="2">
         <v>-119.36167</v>
@@ -4153,8 +4565,11 @@
       <c r="J101" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="102" ht="14.25" customHeight="1">
+      <c r="K101" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>164</v>
       </c>
@@ -4173,16 +4588,19 @@
         <v>214</v>
       </c>
       <c r="H102" s="2">
-        <v>34.01556</v>
+        <v>34.015560000000001</v>
       </c>
       <c r="I102" s="2">
-        <v>-119.36083</v>
+        <v>-119.36083000000001</v>
       </c>
       <c r="J102" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="103" ht="14.25" customHeight="1">
+      <c r="K102" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>86</v>
       </c>
@@ -4201,16 +4619,19 @@
         <v>215</v>
       </c>
       <c r="H103" s="2">
-        <v>34.01556</v>
+        <v>34.015560000000001</v>
       </c>
       <c r="I103" s="2">
-        <v>-119.36056</v>
+        <v>-119.36056000000001</v>
       </c>
       <c r="J103" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="104" ht="14.25" customHeight="1">
+      <c r="K103" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>216</v>
       </c>
@@ -4229,7 +4650,7 @@
         <v>217</v>
       </c>
       <c r="H104" s="2">
-        <v>33.91834683</v>
+        <v>33.918346829999997</v>
       </c>
       <c r="I104" s="2">
         <v>-120.1458535</v>
@@ -4237,8 +4658,11 @@
       <c r="J104" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="105" ht="14.25" customHeight="1">
+      <c r="K104" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>16</v>
       </c>
@@ -4257,7 +4681,7 @@
         <v>218</v>
       </c>
       <c r="H105" s="2">
-        <v>33.91834683</v>
+        <v>33.918346829999997</v>
       </c>
       <c r="I105" s="2">
         <v>-120.1458535</v>
@@ -4265,8 +4689,11 @@
       <c r="J105" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="106" ht="14.25" customHeight="1">
+      <c r="K105" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>29</v>
       </c>
@@ -4285,7 +4712,7 @@
         <v>219</v>
       </c>
       <c r="H106" s="2">
-        <v>33.91834683</v>
+        <v>33.918346829999997</v>
       </c>
       <c r="I106" s="2">
         <v>-120.1458535</v>
@@ -4293,8 +4720,11 @@
       <c r="J106" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="107" ht="14.25" customHeight="1">
+      <c r="K106" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>146</v>
       </c>
@@ -4313,7 +4743,7 @@
         <v>220</v>
       </c>
       <c r="H107" s="2">
-        <v>34.005157</v>
+        <v>34.005156999999997</v>
       </c>
       <c r="I107" s="2">
         <v>-120.178563</v>
@@ -4321,8 +4751,11 @@
       <c r="J107" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="108" ht="14.25" customHeight="1">
+      <c r="K107" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>113</v>
       </c>
@@ -4341,16 +4774,19 @@
         <v>221</v>
       </c>
       <c r="H108" s="2">
-        <v>33.47493</v>
+        <v>33.474930000000001</v>
       </c>
       <c r="I108" s="2">
-        <v>-119.03821</v>
+        <v>-119.03821000000001</v>
       </c>
       <c r="J108" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="109" ht="14.25" customHeight="1">
+      <c r="K108" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>198</v>
       </c>
@@ -4369,16 +4805,19 @@
         <v>222</v>
       </c>
       <c r="H109" s="2">
-        <v>33.47493</v>
+        <v>33.474930000000001</v>
       </c>
       <c r="I109" s="2">
-        <v>-119.03821</v>
+        <v>-119.03821000000001</v>
       </c>
       <c r="J109" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="110" ht="14.25" customHeight="1">
+      <c r="K109" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>123</v>
       </c>
@@ -4397,16 +4836,19 @@
         <v>223</v>
       </c>
       <c r="H110" s="2">
-        <v>33.47493</v>
+        <v>33.474930000000001</v>
       </c>
       <c r="I110" s="2">
-        <v>-119.03821</v>
+        <v>-119.03821000000001</v>
       </c>
       <c r="J110" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="111" ht="14.25" customHeight="1">
+      <c r="K110" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>88</v>
       </c>
@@ -4425,7 +4867,7 @@
         <v>224</v>
       </c>
       <c r="H111" s="2">
-        <v>34.01528</v>
+        <v>34.015279999999997</v>
       </c>
       <c r="I111" s="2">
         <v>-119.36194</v>
@@ -4433,8 +4875,11 @@
       <c r="J111" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="112" ht="14.25" customHeight="1">
+      <c r="K111" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>148</v>
       </c>
@@ -4453,7 +4898,7 @@
         <v>225</v>
       </c>
       <c r="H112" s="2">
-        <v>34.01583</v>
+        <v>34.015830000000001</v>
       </c>
       <c r="I112" s="2">
         <v>-119.36028</v>
@@ -4461,8 +4906,11 @@
       <c r="J112" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="113" ht="14.25" customHeight="1">
+      <c r="K112" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>90</v>
       </c>
@@ -4489,8 +4937,11 @@
       <c r="J113" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="114" ht="14.25" customHeight="1">
+      <c r="K113" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>93</v>
       </c>
@@ -4517,8 +4968,11 @@
       <c r="J114" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="115" ht="14.25" customHeight="1">
+      <c r="K114" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>228</v>
       </c>
@@ -4545,8 +4999,11 @@
       <c r="J115" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="116" ht="14.25" customHeight="1">
+      <c r="K115" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2"/>
       <c r="B116" s="1" t="s">
         <v>29</v>
@@ -4573,8 +5030,11 @@
       <c r="J116" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="117" ht="14.25" customHeight="1">
+      <c r="K116" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
         <v>83</v>
       </c>
@@ -4591,7 +5051,7 @@
         <v>231</v>
       </c>
       <c r="H117" s="7">
-        <v>-33.6261</v>
+        <v>-33.626100000000001</v>
       </c>
       <c r="I117" s="7">
         <v>22.10913</v>
@@ -4599,8 +5059,11 @@
       <c r="J117" s="1" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="118" ht="14.25" customHeight="1">
+      <c r="K117" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
         <v>62</v>
       </c>
@@ -4617,7 +5080,7 @@
         <v>233</v>
       </c>
       <c r="H118" s="7">
-        <v>-33.6261</v>
+        <v>-33.626100000000001</v>
       </c>
       <c r="I118" s="7">
         <v>22.10913</v>
@@ -4625,11 +5088,14 @@
       <c r="J118" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K118" s="1" t="s">
+      <c r="K118" t="s">
+        <v>367</v>
+      </c>
+      <c r="L118" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="119" ht="14.25" customHeight="1">
+    <row r="119" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
         <v>81</v>
       </c>
@@ -4646,7 +5112,7 @@
         <v>235</v>
       </c>
       <c r="H119" s="7">
-        <v>-33.6261</v>
+        <v>-33.626100000000001</v>
       </c>
       <c r="I119" s="7">
         <v>22.10913</v>
@@ -4654,11 +5120,14 @@
       <c r="J119" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K119" s="1" t="s">
+      <c r="K119" t="s">
+        <v>367</v>
+      </c>
+      <c r="L119" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="120" ht="14.25" customHeight="1">
+    <row r="120" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
         <v>104</v>
       </c>
@@ -4675,7 +5144,7 @@
         <v>236</v>
       </c>
       <c r="H120" s="7">
-        <v>-33.6261</v>
+        <v>-33.626100000000001</v>
       </c>
       <c r="I120" s="7">
         <v>22.10913</v>
@@ -4683,11 +5152,14 @@
       <c r="J120" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K120" s="1" t="s">
+      <c r="K120" t="s">
+        <v>367</v>
+      </c>
+      <c r="L120" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="121" ht="14.25" customHeight="1">
+    <row r="121" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
         <v>194</v>
       </c>
@@ -4704,19 +5176,22 @@
         <v>237</v>
       </c>
       <c r="H121" s="7">
-        <v>-33.4484</v>
+        <v>-33.448399999999999</v>
       </c>
       <c r="I121" s="7">
-        <v>25.48108</v>
+        <v>25.481079999999999</v>
       </c>
       <c r="J121" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="K121" s="1" t="s">
+      <c r="K121" t="s">
+        <v>354</v>
+      </c>
+      <c r="L121" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="122" ht="14.25" customHeight="1">
+    <row r="122" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
         <v>47</v>
       </c>
@@ -4733,19 +5208,22 @@
         <v>240</v>
       </c>
       <c r="H122" s="7">
-        <v>-33.4484</v>
+        <v>-33.448399999999999</v>
       </c>
       <c r="I122" s="7">
-        <v>25.48108</v>
+        <v>25.481079999999999</v>
       </c>
       <c r="J122" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="K122" s="1" t="s">
+      <c r="K122" t="s">
+        <v>354</v>
+      </c>
+      <c r="L122" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="123" ht="14.25" customHeight="1">
+    <row r="123" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
         <v>39</v>
       </c>
@@ -4762,19 +5240,22 @@
         <v>241</v>
       </c>
       <c r="H123" s="7">
-        <v>-33.4484</v>
+        <v>-33.448399999999999</v>
       </c>
       <c r="I123" s="7">
-        <v>25.48108</v>
+        <v>25.481079999999999</v>
       </c>
       <c r="J123" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="K123" s="1" t="s">
+      <c r="K123" t="s">
+        <v>354</v>
+      </c>
+      <c r="L123" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="124" ht="14.25" customHeight="1">
+    <row r="124" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6" t="s">
         <v>242</v>
       </c>
@@ -4791,7 +5272,7 @@
         <v>243</v>
       </c>
       <c r="H124" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="I124" s="7">
         <v>18.24061</v>
@@ -4799,11 +5280,14 @@
       <c r="J124" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K124" s="1" t="s">
+      <c r="K124" t="s">
+        <v>355</v>
+      </c>
+      <c r="L124" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="125" ht="14.25" customHeight="1">
+    <row r="125" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6" t="s">
         <v>32</v>
       </c>
@@ -4820,7 +5304,7 @@
         <v>246</v>
       </c>
       <c r="H125" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="I125" s="7">
         <v>18.24061</v>
@@ -4828,11 +5312,14 @@
       <c r="J125" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K125" s="1" t="s">
+      <c r="K125" t="s">
+        <v>355</v>
+      </c>
+      <c r="L125" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="126" ht="14.25" customHeight="1">
+    <row r="126" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6" t="s">
         <v>67</v>
       </c>
@@ -4849,7 +5336,7 @@
         <v>247</v>
       </c>
       <c r="H126" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="I126" s="7">
         <v>18.24061</v>
@@ -4857,11 +5344,14 @@
       <c r="J126" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K126" s="1" t="s">
+      <c r="K126" t="s">
+        <v>355</v>
+      </c>
+      <c r="L126" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="127" ht="14.25" customHeight="1">
+    <row r="127" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6" t="s">
         <v>76</v>
       </c>
@@ -4878,7 +5368,7 @@
         <v>248</v>
       </c>
       <c r="H127" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="I127" s="7">
         <v>18.24061</v>
@@ -4886,11 +5376,14 @@
       <c r="J127" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K127" s="1" t="s">
+      <c r="K127" t="s">
+        <v>355</v>
+      </c>
+      <c r="L127" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="128" ht="14.25" customHeight="1">
+    <row r="128" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6" t="s">
         <v>150</v>
       </c>
@@ -4907,7 +5400,7 @@
         <v>249</v>
       </c>
       <c r="H128" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="I128" s="7">
         <v>18.24061</v>
@@ -4915,11 +5408,14 @@
       <c r="J128" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K128" s="1" t="s">
+      <c r="K128" t="s">
+        <v>355</v>
+      </c>
+      <c r="L128" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="129" ht="14.25" customHeight="1">
+    <row r="129" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6" t="s">
         <v>65</v>
       </c>
@@ -4936,7 +5432,7 @@
         <v>250</v>
       </c>
       <c r="H129" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="I129" s="7">
         <v>18.24061</v>
@@ -4944,11 +5440,14 @@
       <c r="J129" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K129" s="1" t="s">
+      <c r="K129" t="s">
+        <v>355</v>
+      </c>
+      <c r="L129" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="130" ht="14.25" customHeight="1">
+    <row r="130" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6" t="s">
         <v>251</v>
       </c>
@@ -4965,7 +5464,7 @@
         <v>252</v>
       </c>
       <c r="H130" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="I130" s="7">
         <v>18.24061</v>
@@ -4973,11 +5472,14 @@
       <c r="J130" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K130" s="1" t="s">
+      <c r="K130" t="s">
+        <v>355</v>
+      </c>
+      <c r="L130" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="131" ht="14.25" customHeight="1">
+    <row r="131" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6" t="s">
         <v>253</v>
       </c>
@@ -4994,7 +5496,7 @@
         <v>254</v>
       </c>
       <c r="H131" s="7">
-        <v>-33.6332</v>
+        <v>-33.633200000000002</v>
       </c>
       <c r="I131" s="7">
         <v>22.21603</v>
@@ -5002,11 +5504,14 @@
       <c r="J131" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K131" s="1" t="s">
+      <c r="K131" t="s">
+        <v>356</v>
+      </c>
+      <c r="L131" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="132" ht="14.25" customHeight="1">
+    <row r="132" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6" t="s">
         <v>74</v>
       </c>
@@ -5023,7 +5528,7 @@
         <v>256</v>
       </c>
       <c r="H132" s="7">
-        <v>-33.6332</v>
+        <v>-33.633200000000002</v>
       </c>
       <c r="I132" s="7">
         <v>22.21603</v>
@@ -5031,11 +5536,14 @@
       <c r="J132" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K132" s="1" t="s">
+      <c r="K132" t="s">
+        <v>356</v>
+      </c>
+      <c r="L132" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="133" ht="14.25" customHeight="1">
+    <row r="133" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6" t="s">
         <v>79</v>
       </c>
@@ -5052,7 +5560,7 @@
         <v>257</v>
       </c>
       <c r="H133" s="7">
-        <v>-33.6332</v>
+        <v>-33.633200000000002</v>
       </c>
       <c r="I133" s="7">
         <v>22.21603</v>
@@ -5060,11 +5568,14 @@
       <c r="J133" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K133" s="1" t="s">
+      <c r="K133" t="s">
+        <v>356</v>
+      </c>
+      <c r="L133" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="134" ht="14.25" customHeight="1">
+    <row r="134" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
         <v>72</v>
       </c>
@@ -5081,7 +5592,7 @@
         <v>258</v>
       </c>
       <c r="H134" s="7">
-        <v>-33.6332</v>
+        <v>-33.633200000000002</v>
       </c>
       <c r="I134" s="7">
         <v>22.21603</v>
@@ -5089,11 +5600,14 @@
       <c r="J134" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K134" s="1" t="s">
+      <c r="K134" t="s">
+        <v>356</v>
+      </c>
+      <c r="L134" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="135" ht="14.25" customHeight="1">
+    <row r="135" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
         <v>259</v>
       </c>
@@ -5110,19 +5624,22 @@
         <v>260</v>
       </c>
       <c r="H135" s="7">
-        <v>-31.7569</v>
+        <v>-31.756900000000002</v>
       </c>
       <c r="I135" s="7">
-        <v>18.22694</v>
+        <v>18.226939999999999</v>
       </c>
       <c r="J135" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K135" s="1" t="s">
+      <c r="K135" t="s">
+        <v>357</v>
+      </c>
+      <c r="L135" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="136" ht="14.25" customHeight="1">
+    <row r="136" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
         <v>153</v>
       </c>
@@ -5139,19 +5656,22 @@
         <v>262</v>
       </c>
       <c r="H136" s="7">
-        <v>-31.7569</v>
+        <v>-31.756900000000002</v>
       </c>
       <c r="I136" s="7">
-        <v>18.22694</v>
+        <v>18.226939999999999</v>
       </c>
       <c r="J136" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K136" s="1" t="s">
+      <c r="K136" t="s">
+        <v>357</v>
+      </c>
+      <c r="L136" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="137" ht="14.25" customHeight="1">
+    <row r="137" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6" t="s">
         <v>102</v>
       </c>
@@ -5168,19 +5688,22 @@
         <v>263</v>
       </c>
       <c r="H137" s="7">
-        <v>-31.7569</v>
+        <v>-31.756900000000002</v>
       </c>
       <c r="I137" s="7">
-        <v>18.22694</v>
+        <v>18.226939999999999</v>
       </c>
       <c r="J137" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K137" s="1" t="s">
+      <c r="K137" t="s">
+        <v>357</v>
+      </c>
+      <c r="L137" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="138" ht="14.25" customHeight="1">
+    <row r="138" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6" t="s">
         <v>264</v>
       </c>
@@ -5197,19 +5720,22 @@
         <v>265</v>
       </c>
       <c r="H138" s="7">
-        <v>-31.5267</v>
+        <v>-31.526700000000002</v>
       </c>
       <c r="I138" s="7">
-        <v>18.86556</v>
+        <v>18.865559999999999</v>
       </c>
       <c r="J138" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K138" s="1" t="s">
+      <c r="K138" t="s">
+        <v>358</v>
+      </c>
+      <c r="L138" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="139" ht="14.25" customHeight="1">
+    <row r="139" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6" t="s">
         <v>137</v>
       </c>
@@ -5226,19 +5752,22 @@
         <v>268</v>
       </c>
       <c r="H139" s="7">
-        <v>-31.5267</v>
+        <v>-31.526700000000002</v>
       </c>
       <c r="I139" s="7">
-        <v>18.86556</v>
+        <v>18.865559999999999</v>
       </c>
       <c r="J139" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K139" s="1" t="s">
+      <c r="K139" t="s">
+        <v>358</v>
+      </c>
+      <c r="L139" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="140" ht="14.25" customHeight="1">
+    <row r="140" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6" t="s">
         <v>109</v>
       </c>
@@ -5255,19 +5784,22 @@
         <v>269</v>
       </c>
       <c r="H140" s="7">
-        <v>-31.5267</v>
+        <v>-31.526700000000002</v>
       </c>
       <c r="I140" s="7">
-        <v>18.86556</v>
+        <v>18.865559999999999</v>
       </c>
       <c r="J140" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K140" s="1" t="s">
+      <c r="K140" t="s">
+        <v>358</v>
+      </c>
+      <c r="L140" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="141" ht="14.25" customHeight="1">
+    <row r="141" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6" t="s">
         <v>270</v>
       </c>
@@ -5284,7 +5816,7 @@
         <v>271</v>
       </c>
       <c r="H141" s="7">
-        <v>-31.4658</v>
+        <v>-31.465800000000002</v>
       </c>
       <c r="I141" s="7">
         <v>19.78556</v>
@@ -5292,11 +5824,14 @@
       <c r="J141" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K141" s="1" t="s">
+      <c r="K141" t="s">
+        <v>359</v>
+      </c>
+      <c r="L141" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="142" ht="14.25" customHeight="1">
+    <row r="142" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
         <v>49</v>
       </c>
@@ -5313,7 +5848,7 @@
         <v>273</v>
       </c>
       <c r="H142" s="7">
-        <v>-31.4658</v>
+        <v>-31.465800000000002</v>
       </c>
       <c r="I142" s="7">
         <v>19.78556</v>
@@ -5321,11 +5856,14 @@
       <c r="J142" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K142" s="1" t="s">
+      <c r="K142" t="s">
+        <v>359</v>
+      </c>
+      <c r="L142" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="143" ht="14.25" customHeight="1">
+    <row r="143" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
         <v>128</v>
       </c>
@@ -5342,7 +5880,7 @@
         <v>274</v>
       </c>
       <c r="H143" s="7">
-        <v>-31.4658</v>
+        <v>-31.465800000000002</v>
       </c>
       <c r="I143" s="7">
         <v>19.78556</v>
@@ -5350,11 +5888,14 @@
       <c r="J143" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K143" s="1" t="s">
+      <c r="K143" t="s">
+        <v>359</v>
+      </c>
+      <c r="L143" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="144" ht="14.25" customHeight="1">
+    <row r="144" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
         <v>53</v>
       </c>
@@ -5374,16 +5915,19 @@
         <v>-30.3461</v>
       </c>
       <c r="I144" s="7">
-        <v>17.28306</v>
+        <v>17.283059999999999</v>
       </c>
       <c r="J144" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K144" s="1" t="s">
+      <c r="K144" t="s">
+        <v>360</v>
+      </c>
+      <c r="L144" s="1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="145" ht="14.25" customHeight="1">
+    <row r="145" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6" t="s">
         <v>277</v>
       </c>
@@ -5403,16 +5947,19 @@
         <v>-30.3461</v>
       </c>
       <c r="I145" s="7">
-        <v>17.28306</v>
+        <v>17.283059999999999</v>
       </c>
       <c r="J145" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K145" s="1" t="s">
+      <c r="K145" t="s">
+        <v>360</v>
+      </c>
+      <c r="L145" s="1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="146" ht="14.25" customHeight="1">
+    <row r="146" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6" t="s">
         <v>121</v>
       </c>
@@ -5429,19 +5976,22 @@
         <v>279</v>
       </c>
       <c r="H146" s="7">
-        <v>-29.6786</v>
+        <v>-29.678599999999999</v>
       </c>
       <c r="I146" s="7">
-        <v>17.06167</v>
+        <v>17.061669999999999</v>
       </c>
       <c r="J146" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K146" s="1" t="s">
+      <c r="K146" t="s">
+        <v>361</v>
+      </c>
+      <c r="L146" s="1" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="147" ht="14.25" customHeight="1">
+    <row r="147" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6" t="s">
         <v>281</v>
       </c>
@@ -5458,19 +6008,22 @@
         <v>282</v>
       </c>
       <c r="H147" s="7">
-        <v>-29.6786</v>
+        <v>-29.678599999999999</v>
       </c>
       <c r="I147" s="7">
-        <v>17.06167</v>
+        <v>17.061669999999999</v>
       </c>
       <c r="J147" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K147" s="1" t="s">
+      <c r="K147" t="s">
+        <v>361</v>
+      </c>
+      <c r="L147" s="1" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="148" ht="14.25" customHeight="1">
+    <row r="148" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
         <v>283</v>
       </c>
@@ -5490,16 +6043,19 @@
         <v>-33.0608</v>
       </c>
       <c r="I148" s="7">
-        <v>18.04283</v>
+        <v>18.042829999999999</v>
       </c>
       <c r="J148" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K148" s="1" t="s">
+      <c r="K148" t="s">
+        <v>362</v>
+      </c>
+      <c r="L148" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="149" ht="14.25" customHeight="1">
+    <row r="149" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
         <v>286</v>
       </c>
@@ -5519,16 +6075,19 @@
         <v>-33.0608</v>
       </c>
       <c r="I149" s="7">
-        <v>18.04283</v>
+        <v>18.042829999999999</v>
       </c>
       <c r="J149" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K149" s="1" t="s">
+      <c r="K149" t="s">
+        <v>362</v>
+      </c>
+      <c r="L149" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="150" ht="14.25" customHeight="1">
+    <row r="150" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
         <v>288</v>
       </c>
@@ -5545,19 +6104,22 @@
         <v>289</v>
       </c>
       <c r="H150" s="7">
-        <v>-33.6831</v>
+        <v>-33.683100000000003</v>
       </c>
       <c r="I150" s="7">
-        <v>19.59444</v>
+        <v>19.594439999999999</v>
       </c>
       <c r="J150" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K150" s="1" t="s">
+      <c r="K150" t="s">
+        <v>363</v>
+      </c>
+      <c r="L150" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="151" ht="14.25" customHeight="1">
+    <row r="151" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
         <v>291</v>
       </c>
@@ -5574,19 +6136,22 @@
         <v>292</v>
       </c>
       <c r="H151" s="7">
-        <v>-33.6831</v>
+        <v>-33.683100000000003</v>
       </c>
       <c r="I151" s="7">
-        <v>19.59444</v>
+        <v>19.594439999999999</v>
       </c>
       <c r="J151" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K151" s="1" t="s">
+      <c r="K151" t="s">
+        <v>363</v>
+      </c>
+      <c r="L151" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="152" ht="14.25" customHeight="1">
+    <row r="152" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
         <v>143</v>
       </c>
@@ -5603,19 +6168,22 @@
         <v>293</v>
       </c>
       <c r="H152" s="7">
-        <v>-33.6831</v>
+        <v>-33.683100000000003</v>
       </c>
       <c r="I152" s="7">
-        <v>19.59444</v>
+        <v>19.594439999999999</v>
       </c>
       <c r="J152" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K152" s="1" t="s">
+      <c r="K152" t="s">
+        <v>363</v>
+      </c>
+      <c r="L152" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="153" ht="14.25" customHeight="1">
+    <row r="153" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B153" s="6" t="s">
         <v>207</v>
       </c>
@@ -5632,19 +6200,22 @@
         <v>294</v>
       </c>
       <c r="H153" s="7">
-        <v>-33.4484</v>
+        <v>-33.448399999999999</v>
       </c>
       <c r="I153" s="7">
-        <v>25.48108</v>
+        <v>25.481079999999999</v>
       </c>
       <c r="J153" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="K153" s="1" t="s">
+      <c r="K153" t="s">
+        <v>354</v>
+      </c>
+      <c r="L153" s="1" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="154" ht="14.25" customHeight="1">
+    <row r="154" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B154" s="6" t="s">
         <v>18</v>
       </c>
@@ -5661,19 +6232,22 @@
         <v>296</v>
       </c>
       <c r="H154" s="7">
-        <v>-33.4484</v>
+        <v>-33.448399999999999</v>
       </c>
       <c r="I154" s="7">
-        <v>25.48108</v>
+        <v>25.481079999999999</v>
       </c>
       <c r="J154" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="K154" s="1" t="s">
+      <c r="K154" t="s">
+        <v>354</v>
+      </c>
+      <c r="L154" s="1" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="155" ht="14.25" customHeight="1">
+    <row r="155" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B155" s="6" t="s">
         <v>171</v>
       </c>
@@ -5690,7 +6264,7 @@
         <v>297</v>
       </c>
       <c r="H155" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="I155" s="7">
         <v>18.24061</v>
@@ -5698,11 +6272,14 @@
       <c r="J155" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="K155" s="1" t="s">
+      <c r="K155" t="s">
+        <v>355</v>
+      </c>
+      <c r="L155" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="156" ht="14.25" customHeight="1">
+    <row r="156" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B156" s="6" t="s">
         <v>128</v>
       </c>
@@ -5719,7 +6296,7 @@
         <v>298</v>
       </c>
       <c r="H156" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="I156" s="7">
         <v>18.24061</v>
@@ -5727,11 +6304,14 @@
       <c r="J156" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K156" s="1" t="s">
+      <c r="K156" t="s">
+        <v>355</v>
+      </c>
+      <c r="L156" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="157" ht="14.25" customHeight="1">
+    <row r="157" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B157" s="6" t="s">
         <v>283</v>
       </c>
@@ -5748,7 +6328,7 @@
         <v>299</v>
       </c>
       <c r="H157" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="I157" s="7">
         <v>18.24061</v>
@@ -5756,11 +6336,14 @@
       <c r="J157" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K157" s="1" t="s">
+      <c r="K157" t="s">
+        <v>355</v>
+      </c>
+      <c r="L157" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="158" ht="14.25" customHeight="1">
+    <row r="158" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B158" s="6" t="s">
         <v>107</v>
       </c>
@@ -5777,7 +6360,7 @@
         <v>300</v>
       </c>
       <c r="H158" s="7">
-        <v>-33.6332</v>
+        <v>-33.633200000000002</v>
       </c>
       <c r="I158" s="7">
         <v>22.21603</v>
@@ -5785,11 +6368,14 @@
       <c r="J158" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K158" s="1" t="s">
+      <c r="K158" t="s">
+        <v>356</v>
+      </c>
+      <c r="L158" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="159" ht="14.25" customHeight="1">
+    <row r="159" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B159" s="6" t="s">
         <v>55</v>
       </c>
@@ -5806,19 +6392,22 @@
         <v>301</v>
       </c>
       <c r="H159" s="7">
-        <v>-31.7569</v>
+        <v>-31.756900000000002</v>
       </c>
       <c r="I159" s="7">
-        <v>18.22694</v>
+        <v>18.226939999999999</v>
       </c>
       <c r="J159" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K159" s="1" t="s">
+      <c r="K159" t="s">
+        <v>357</v>
+      </c>
+      <c r="L159" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="160" ht="14.25" customHeight="1">
+    <row r="160" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B160" s="6" t="s">
         <v>10</v>
       </c>
@@ -5835,19 +6424,22 @@
         <v>302</v>
       </c>
       <c r="H160" s="7">
-        <v>-31.7569</v>
+        <v>-31.756900000000002</v>
       </c>
       <c r="I160" s="7">
-        <v>18.22694</v>
+        <v>18.226939999999999</v>
       </c>
       <c r="J160" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K160" s="1" t="s">
+      <c r="K160" t="s">
+        <v>358</v>
+      </c>
+      <c r="L160" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="161" ht="14.25" customHeight="1">
+    <row r="161" spans="2:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B161" s="6" t="s">
         <v>76</v>
       </c>
@@ -5864,19 +6456,22 @@
         <v>303</v>
       </c>
       <c r="H161" s="7">
-        <v>-31.5267</v>
+        <v>-31.526700000000002</v>
       </c>
       <c r="I161" s="7">
-        <v>18.86556</v>
+        <v>18.865559999999999</v>
       </c>
       <c r="J161" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K161" s="1" t="s">
+      <c r="K161" t="s">
+        <v>358</v>
+      </c>
+      <c r="L161" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="162" ht="14.25" customHeight="1">
+    <row r="162" spans="2:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B162" s="6" t="s">
         <v>228</v>
       </c>
@@ -5893,19 +6488,22 @@
         <v>304</v>
       </c>
       <c r="H162" s="7">
-        <v>-31.5267</v>
+        <v>-31.526700000000002</v>
       </c>
       <c r="I162" s="7">
-        <v>18.86556</v>
+        <v>18.865559999999999</v>
       </c>
       <c r="J162" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K162" s="1" t="s">
+      <c r="K162" t="s">
+        <v>358</v>
+      </c>
+      <c r="L162" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="163" ht="14.25" customHeight="1">
+    <row r="163" spans="2:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B163" s="6" t="s">
         <v>153</v>
       </c>
@@ -5922,7 +6520,7 @@
         <v>305</v>
       </c>
       <c r="H163" s="7">
-        <v>-31.4658</v>
+        <v>-31.465800000000002</v>
       </c>
       <c r="I163" s="7">
         <v>19.78556</v>
@@ -5930,11 +6528,14 @@
       <c r="J163" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K163" s="1" t="s">
+      <c r="K163" t="s">
+        <v>359</v>
+      </c>
+      <c r="L163" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="164" ht="14.25" customHeight="1">
+    <row r="164" spans="2:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B164" s="6" t="s">
         <v>88</v>
       </c>
@@ -5951,7 +6552,7 @@
         <v>306</v>
       </c>
       <c r="H164" s="7">
-        <v>-31.4658</v>
+        <v>-31.465800000000002</v>
       </c>
       <c r="I164" s="7">
         <v>19.78556</v>
@@ -5959,11 +6560,14 @@
       <c r="J164" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K164" s="1" t="s">
+      <c r="K164" t="s">
+        <v>359</v>
+      </c>
+      <c r="L164" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="165" ht="14.25" customHeight="1">
+    <row r="165" spans="2:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B165" s="6" t="s">
         <v>201</v>
       </c>
@@ -5983,16 +6587,19 @@
         <v>-30.3461</v>
       </c>
       <c r="I165" s="7">
-        <v>17.28306</v>
+        <v>17.283059999999999</v>
       </c>
       <c r="J165" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K165" s="1" t="s">
+      <c r="K165" t="s">
+        <v>360</v>
+      </c>
+      <c r="L165" s="1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="166" ht="14.25" customHeight="1">
+    <row r="166" spans="2:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B166" s="6" t="s">
         <v>146</v>
       </c>
@@ -6012,16 +6619,19 @@
         <v>-30.3461</v>
       </c>
       <c r="I166" s="7">
-        <v>17.28306</v>
+        <v>17.283059999999999</v>
       </c>
       <c r="J166" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K166" s="1" t="s">
+      <c r="K166" t="s">
+        <v>360</v>
+      </c>
+      <c r="L166" s="1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="167" ht="14.25" customHeight="1">
+    <row r="167" spans="2:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="6" t="s">
         <v>119</v>
       </c>
@@ -6041,16 +6651,19 @@
         <v>-30.3461</v>
       </c>
       <c r="I167" s="7">
-        <v>17.28306</v>
+        <v>17.283059999999999</v>
       </c>
       <c r="J167" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K167" s="1" t="s">
+      <c r="K167" t="s">
+        <v>360</v>
+      </c>
+      <c r="L167" s="1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="168" ht="14.25" customHeight="1">
+    <row r="168" spans="2:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B168" s="6" t="s">
         <v>310</v>
       </c>
@@ -6067,19 +6680,22 @@
         <v>311</v>
       </c>
       <c r="H168" s="7">
-        <v>-29.6786</v>
+        <v>-29.678599999999999</v>
       </c>
       <c r="I168" s="7">
-        <v>17.06167</v>
+        <v>17.061669999999999</v>
       </c>
       <c r="J168" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K168" s="1" t="s">
+      <c r="K168" t="s">
+        <v>361</v>
+      </c>
+      <c r="L168" s="1" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="169" ht="14.25" customHeight="1">
+    <row r="169" spans="2:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B169" s="6" t="s">
         <v>135</v>
       </c>
@@ -6096,19 +6712,22 @@
         <v>312</v>
       </c>
       <c r="H169" s="7">
-        <v>-29.6786</v>
+        <v>-29.678599999999999</v>
       </c>
       <c r="I169" s="7">
-        <v>17.06167</v>
+        <v>17.061669999999999</v>
       </c>
       <c r="J169" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K169" s="1" t="s">
+      <c r="K169" t="s">
+        <v>361</v>
+      </c>
+      <c r="L169" s="1" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="170" ht="14.25" customHeight="1">
+    <row r="170" spans="2:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B170" s="6" t="s">
         <v>123</v>
       </c>
@@ -6128,16 +6747,19 @@
         <v>-33.0608</v>
       </c>
       <c r="I170" s="7">
-        <v>18.04283</v>
+        <v>18.042829999999999</v>
       </c>
       <c r="J170" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K170" s="1" t="s">
+      <c r="K170" t="s">
+        <v>362</v>
+      </c>
+      <c r="L170" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="171" ht="14.25" customHeight="1">
+    <row r="171" spans="2:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B171" s="6" t="s">
         <v>34</v>
       </c>
@@ -6154,19 +6776,22 @@
         <v>314</v>
       </c>
       <c r="H171" s="7">
-        <v>-33.6831</v>
+        <v>-33.683100000000003</v>
       </c>
       <c r="I171" s="7">
-        <v>19.59444</v>
+        <v>19.594439999999999</v>
       </c>
       <c r="J171" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K171" s="1" t="s">
+      <c r="K171" t="s">
+        <v>363</v>
+      </c>
+      <c r="L171" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="172" ht="14.25" customHeight="1">
+    <row r="172" spans="2:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B172" s="6" t="s">
         <v>113</v>
       </c>
@@ -6183,1164 +6808,1167 @@
         <v>315</v>
       </c>
       <c r="H172" s="7">
-        <v>-33.6831</v>
+        <v>-33.683100000000003</v>
       </c>
       <c r="I172" s="7">
-        <v>19.59444</v>
+        <v>19.594439999999999</v>
       </c>
       <c r="J172" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K172" s="1" t="s">
+      <c r="K172" t="s">
+        <v>363</v>
+      </c>
+      <c r="L172" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="173" ht="14.25" customHeight="1"/>
-    <row r="174" ht="14.25" customHeight="1"/>
-    <row r="175" ht="14.25" customHeight="1"/>
-    <row r="176" ht="14.25" customHeight="1"/>
-    <row r="177" ht="14.25" customHeight="1"/>
-    <row r="178" ht="14.25" customHeight="1"/>
-    <row r="179" ht="14.25" customHeight="1"/>
-    <row r="180" ht="14.25" customHeight="1"/>
-    <row r="181" ht="14.25" customHeight="1"/>
-    <row r="182" ht="14.25" customHeight="1"/>
-    <row r="183" ht="14.25" customHeight="1"/>
-    <row r="184" ht="14.25" customHeight="1"/>
-    <row r="185" ht="14.25" customHeight="1"/>
-    <row r="186" ht="14.25" customHeight="1"/>
-    <row r="187" ht="14.25" customHeight="1"/>
-    <row r="188" ht="14.25" customHeight="1"/>
-    <row r="189" ht="14.25" customHeight="1"/>
-    <row r="190" ht="14.25" customHeight="1"/>
-    <row r="191" ht="14.25" customHeight="1"/>
-    <row r="192" ht="14.25" customHeight="1"/>
-    <row r="193" ht="14.25" customHeight="1"/>
-    <row r="194" ht="14.25" customHeight="1"/>
-    <row r="195" ht="14.25" customHeight="1"/>
-    <row r="196" ht="14.25" customHeight="1"/>
-    <row r="197" ht="14.25" customHeight="1"/>
-    <row r="198" ht="14.25" customHeight="1"/>
-    <row r="199" ht="14.25" customHeight="1"/>
-    <row r="200" ht="14.25" customHeight="1"/>
-    <row r="201" ht="14.25" customHeight="1"/>
-    <row r="202" ht="14.25" customHeight="1"/>
-    <row r="203" ht="14.25" customHeight="1"/>
-    <row r="204" ht="14.25" customHeight="1"/>
-    <row r="205" ht="14.25" customHeight="1"/>
-    <row r="206" ht="14.25" customHeight="1"/>
-    <row r="207" ht="14.25" customHeight="1"/>
-    <row r="208" ht="14.25" customHeight="1"/>
-    <row r="209" ht="14.25" customHeight="1"/>
-    <row r="210" ht="14.25" customHeight="1"/>
-    <row r="211" ht="14.25" customHeight="1"/>
-    <row r="212" ht="14.25" customHeight="1"/>
-    <row r="213" ht="14.25" customHeight="1"/>
-    <row r="214" ht="14.25" customHeight="1"/>
-    <row r="215" ht="14.25" customHeight="1"/>
-    <row r="216" ht="14.25" customHeight="1"/>
-    <row r="217" ht="14.25" customHeight="1"/>
-    <row r="218" ht="14.25" customHeight="1"/>
-    <row r="219" ht="14.25" customHeight="1"/>
-    <row r="220" ht="14.25" customHeight="1"/>
-    <row r="221" ht="14.25" customHeight="1"/>
-    <row r="222" ht="14.25" customHeight="1"/>
-    <row r="223" ht="14.25" customHeight="1"/>
-    <row r="224" ht="14.25" customHeight="1"/>
-    <row r="225" ht="14.25" customHeight="1"/>
-    <row r="226" ht="14.25" customHeight="1"/>
-    <row r="227" ht="14.25" customHeight="1"/>
-    <row r="228" ht="14.25" customHeight="1"/>
-    <row r="229" ht="14.25" customHeight="1"/>
-    <row r="230" ht="14.25" customHeight="1"/>
-    <row r="231" ht="14.25" customHeight="1"/>
-    <row r="232" ht="14.25" customHeight="1"/>
-    <row r="233" ht="14.25" customHeight="1"/>
-    <row r="234" ht="14.25" customHeight="1"/>
-    <row r="235" ht="14.25" customHeight="1"/>
-    <row r="236" ht="14.25" customHeight="1"/>
-    <row r="237" ht="14.25" customHeight="1"/>
-    <row r="238" ht="14.25" customHeight="1"/>
-    <row r="239" ht="14.25" customHeight="1"/>
-    <row r="240" ht="14.25" customHeight="1"/>
-    <row r="241" ht="14.25" customHeight="1"/>
-    <row r="242" ht="14.25" customHeight="1"/>
-    <row r="243" ht="14.25" customHeight="1"/>
-    <row r="244" ht="14.25" customHeight="1"/>
-    <row r="245" ht="14.25" customHeight="1"/>
-    <row r="246" ht="14.25" customHeight="1"/>
-    <row r="247" ht="14.25" customHeight="1"/>
-    <row r="248" ht="14.25" customHeight="1"/>
-    <row r="249" ht="14.25" customHeight="1"/>
-    <row r="250" ht="14.25" customHeight="1"/>
-    <row r="251" ht="14.25" customHeight="1"/>
-    <row r="252" ht="14.25" customHeight="1"/>
-    <row r="253" ht="14.25" customHeight="1"/>
-    <row r="254" ht="14.25" customHeight="1"/>
-    <row r="255" ht="14.25" customHeight="1"/>
-    <row r="256" ht="14.25" customHeight="1"/>
-    <row r="257" ht="14.25" customHeight="1"/>
-    <row r="258" ht="14.25" customHeight="1"/>
-    <row r="259" ht="14.25" customHeight="1"/>
-    <row r="260" ht="14.25" customHeight="1"/>
-    <row r="261" ht="14.25" customHeight="1"/>
-    <row r="262" ht="14.25" customHeight="1"/>
-    <row r="263" ht="14.25" customHeight="1"/>
-    <row r="264" ht="14.25" customHeight="1"/>
-    <row r="265" ht="14.25" customHeight="1"/>
-    <row r="266" ht="14.25" customHeight="1"/>
-    <row r="267" ht="14.25" customHeight="1"/>
-    <row r="268" ht="14.25" customHeight="1"/>
-    <row r="269" ht="14.25" customHeight="1"/>
-    <row r="270" ht="14.25" customHeight="1"/>
-    <row r="271" ht="14.25" customHeight="1"/>
-    <row r="272" ht="14.25" customHeight="1"/>
-    <row r="273" ht="14.25" customHeight="1"/>
-    <row r="274" ht="14.25" customHeight="1"/>
-    <row r="275" ht="14.25" customHeight="1"/>
-    <row r="276" ht="14.25" customHeight="1"/>
-    <row r="277" ht="14.25" customHeight="1"/>
-    <row r="278" ht="14.25" customHeight="1"/>
-    <row r="279" ht="14.25" customHeight="1"/>
-    <row r="280" ht="14.25" customHeight="1"/>
-    <row r="281" ht="14.25" customHeight="1"/>
-    <row r="282" ht="14.25" customHeight="1"/>
-    <row r="283" ht="14.25" customHeight="1"/>
-    <row r="284" ht="14.25" customHeight="1"/>
-    <row r="285" ht="14.25" customHeight="1"/>
-    <row r="286" ht="14.25" customHeight="1"/>
-    <row r="287" ht="14.25" customHeight="1"/>
-    <row r="288" ht="14.25" customHeight="1"/>
-    <row r="289" ht="14.25" customHeight="1"/>
-    <row r="290" ht="14.25" customHeight="1"/>
-    <row r="291" ht="14.25" customHeight="1"/>
-    <row r="292" ht="14.25" customHeight="1"/>
-    <row r="293" ht="14.25" customHeight="1"/>
-    <row r="294" ht="14.25" customHeight="1"/>
-    <row r="295" ht="14.25" customHeight="1"/>
-    <row r="296" ht="14.25" customHeight="1"/>
-    <row r="297" ht="14.25" customHeight="1"/>
-    <row r="298" ht="14.25" customHeight="1"/>
-    <row r="299" ht="14.25" customHeight="1"/>
-    <row r="300" ht="14.25" customHeight="1"/>
-    <row r="301" ht="14.25" customHeight="1"/>
-    <row r="302" ht="14.25" customHeight="1"/>
-    <row r="303" ht="14.25" customHeight="1"/>
-    <row r="304" ht="14.25" customHeight="1"/>
-    <row r="305" ht="14.25" customHeight="1"/>
-    <row r="306" ht="14.25" customHeight="1"/>
-    <row r="307" ht="14.25" customHeight="1"/>
-    <row r="308" ht="14.25" customHeight="1"/>
-    <row r="309" ht="14.25" customHeight="1"/>
-    <row r="310" ht="14.25" customHeight="1"/>
-    <row r="311" ht="14.25" customHeight="1"/>
-    <row r="312" ht="14.25" customHeight="1"/>
-    <row r="313" ht="14.25" customHeight="1"/>
-    <row r="314" ht="14.25" customHeight="1"/>
-    <row r="315" ht="14.25" customHeight="1"/>
-    <row r="316" ht="14.25" customHeight="1"/>
-    <row r="317" ht="14.25" customHeight="1"/>
-    <row r="318" ht="14.25" customHeight="1"/>
-    <row r="319" ht="14.25" customHeight="1"/>
-    <row r="320" ht="14.25" customHeight="1"/>
-    <row r="321" ht="14.25" customHeight="1"/>
-    <row r="322" ht="14.25" customHeight="1"/>
-    <row r="323" ht="14.25" customHeight="1"/>
-    <row r="324" ht="14.25" customHeight="1"/>
-    <row r="325" ht="14.25" customHeight="1"/>
-    <row r="326" ht="14.25" customHeight="1"/>
-    <row r="327" ht="14.25" customHeight="1"/>
-    <row r="328" ht="14.25" customHeight="1"/>
-    <row r="329" ht="14.25" customHeight="1"/>
-    <row r="330" ht="14.25" customHeight="1"/>
-    <row r="331" ht="14.25" customHeight="1"/>
-    <row r="332" ht="14.25" customHeight="1"/>
-    <row r="333" ht="14.25" customHeight="1"/>
-    <row r="334" ht="14.25" customHeight="1"/>
-    <row r="335" ht="14.25" customHeight="1"/>
-    <row r="336" ht="14.25" customHeight="1"/>
-    <row r="337" ht="14.25" customHeight="1"/>
-    <row r="338" ht="14.25" customHeight="1"/>
-    <row r="339" ht="14.25" customHeight="1"/>
-    <row r="340" ht="14.25" customHeight="1"/>
-    <row r="341" ht="14.25" customHeight="1"/>
-    <row r="342" ht="14.25" customHeight="1"/>
-    <row r="343" ht="14.25" customHeight="1"/>
-    <row r="344" ht="14.25" customHeight="1"/>
-    <row r="345" ht="14.25" customHeight="1"/>
-    <row r="346" ht="14.25" customHeight="1"/>
-    <row r="347" ht="14.25" customHeight="1"/>
-    <row r="348" ht="14.25" customHeight="1"/>
-    <row r="349" ht="14.25" customHeight="1"/>
-    <row r="350" ht="14.25" customHeight="1"/>
-    <row r="351" ht="14.25" customHeight="1"/>
-    <row r="352" ht="14.25" customHeight="1"/>
-    <row r="353" ht="14.25" customHeight="1"/>
-    <row r="354" ht="14.25" customHeight="1"/>
-    <row r="355" ht="14.25" customHeight="1"/>
-    <row r="356" ht="14.25" customHeight="1"/>
-    <row r="357" ht="14.25" customHeight="1"/>
-    <row r="358" ht="14.25" customHeight="1"/>
-    <row r="359" ht="14.25" customHeight="1"/>
-    <row r="360" ht="14.25" customHeight="1"/>
-    <row r="361" ht="14.25" customHeight="1"/>
-    <row r="362" ht="14.25" customHeight="1"/>
-    <row r="363" ht="14.25" customHeight="1"/>
-    <row r="364" ht="14.25" customHeight="1"/>
-    <row r="365" ht="14.25" customHeight="1"/>
-    <row r="366" ht="14.25" customHeight="1"/>
-    <row r="367" ht="14.25" customHeight="1"/>
-    <row r="368" ht="14.25" customHeight="1"/>
-    <row r="369" ht="14.25" customHeight="1"/>
-    <row r="370" ht="14.25" customHeight="1"/>
-    <row r="371" ht="14.25" customHeight="1"/>
-    <row r="372" ht="14.25" customHeight="1"/>
-    <row r="373" ht="14.25" customHeight="1"/>
-    <row r="374" ht="14.25" customHeight="1"/>
-    <row r="375" ht="14.25" customHeight="1"/>
-    <row r="376" ht="14.25" customHeight="1"/>
-    <row r="377" ht="14.25" customHeight="1"/>
-    <row r="378" ht="14.25" customHeight="1"/>
-    <row r="379" ht="14.25" customHeight="1"/>
-    <row r="380" ht="14.25" customHeight="1"/>
-    <row r="381" ht="14.25" customHeight="1"/>
-    <row r="382" ht="14.25" customHeight="1"/>
-    <row r="383" ht="14.25" customHeight="1"/>
-    <row r="384" ht="14.25" customHeight="1"/>
-    <row r="385" ht="14.25" customHeight="1"/>
-    <row r="386" ht="14.25" customHeight="1"/>
-    <row r="387" ht="14.25" customHeight="1"/>
-    <row r="388" ht="14.25" customHeight="1"/>
-    <row r="389" ht="14.25" customHeight="1"/>
-    <row r="390" ht="14.25" customHeight="1"/>
-    <row r="391" ht="14.25" customHeight="1"/>
-    <row r="392" ht="14.25" customHeight="1"/>
-    <row r="393" ht="14.25" customHeight="1"/>
-    <row r="394" ht="14.25" customHeight="1"/>
-    <row r="395" ht="14.25" customHeight="1"/>
-    <row r="396" ht="14.25" customHeight="1"/>
-    <row r="397" ht="14.25" customHeight="1"/>
-    <row r="398" ht="14.25" customHeight="1"/>
-    <row r="399" ht="14.25" customHeight="1"/>
-    <row r="400" ht="14.25" customHeight="1"/>
-    <row r="401" ht="14.25" customHeight="1"/>
-    <row r="402" ht="14.25" customHeight="1"/>
-    <row r="403" ht="14.25" customHeight="1"/>
-    <row r="404" ht="14.25" customHeight="1"/>
-    <row r="405" ht="14.25" customHeight="1"/>
-    <row r="406" ht="14.25" customHeight="1"/>
-    <row r="407" ht="14.25" customHeight="1"/>
-    <row r="408" ht="14.25" customHeight="1"/>
-    <row r="409" ht="14.25" customHeight="1"/>
-    <row r="410" ht="14.25" customHeight="1"/>
-    <row r="411" ht="14.25" customHeight="1"/>
-    <row r="412" ht="14.25" customHeight="1"/>
-    <row r="413" ht="14.25" customHeight="1"/>
-    <row r="414" ht="14.25" customHeight="1"/>
-    <row r="415" ht="14.25" customHeight="1"/>
-    <row r="416" ht="14.25" customHeight="1"/>
-    <row r="417" ht="14.25" customHeight="1"/>
-    <row r="418" ht="14.25" customHeight="1"/>
-    <row r="419" ht="14.25" customHeight="1"/>
-    <row r="420" ht="14.25" customHeight="1"/>
-    <row r="421" ht="14.25" customHeight="1"/>
-    <row r="422" ht="14.25" customHeight="1"/>
-    <row r="423" ht="14.25" customHeight="1"/>
-    <row r="424" ht="14.25" customHeight="1"/>
-    <row r="425" ht="14.25" customHeight="1"/>
-    <row r="426" ht="14.25" customHeight="1"/>
-    <row r="427" ht="14.25" customHeight="1"/>
-    <row r="428" ht="14.25" customHeight="1"/>
-    <row r="429" ht="14.25" customHeight="1"/>
-    <row r="430" ht="14.25" customHeight="1"/>
-    <row r="431" ht="14.25" customHeight="1"/>
-    <row r="432" ht="14.25" customHeight="1"/>
-    <row r="433" ht="14.25" customHeight="1"/>
-    <row r="434" ht="14.25" customHeight="1"/>
-    <row r="435" ht="14.25" customHeight="1"/>
-    <row r="436" ht="14.25" customHeight="1"/>
-    <row r="437" ht="14.25" customHeight="1"/>
-    <row r="438" ht="14.25" customHeight="1"/>
-    <row r="439" ht="14.25" customHeight="1"/>
-    <row r="440" ht="14.25" customHeight="1"/>
-    <row r="441" ht="14.25" customHeight="1"/>
-    <row r="442" ht="14.25" customHeight="1"/>
-    <row r="443" ht="14.25" customHeight="1"/>
-    <row r="444" ht="14.25" customHeight="1"/>
-    <row r="445" ht="14.25" customHeight="1"/>
-    <row r="446" ht="14.25" customHeight="1"/>
-    <row r="447" ht="14.25" customHeight="1"/>
-    <row r="448" ht="14.25" customHeight="1"/>
-    <row r="449" ht="14.25" customHeight="1"/>
-    <row r="450" ht="14.25" customHeight="1"/>
-    <row r="451" ht="14.25" customHeight="1"/>
-    <row r="452" ht="14.25" customHeight="1"/>
-    <row r="453" ht="14.25" customHeight="1"/>
-    <row r="454" ht="14.25" customHeight="1"/>
-    <row r="455" ht="14.25" customHeight="1"/>
-    <row r="456" ht="14.25" customHeight="1"/>
-    <row r="457" ht="14.25" customHeight="1"/>
-    <row r="458" ht="14.25" customHeight="1"/>
-    <row r="459" ht="14.25" customHeight="1"/>
-    <row r="460" ht="14.25" customHeight="1"/>
-    <row r="461" ht="14.25" customHeight="1"/>
-    <row r="462" ht="14.25" customHeight="1"/>
-    <row r="463" ht="14.25" customHeight="1"/>
-    <row r="464" ht="14.25" customHeight="1"/>
-    <row r="465" ht="14.25" customHeight="1"/>
-    <row r="466" ht="14.25" customHeight="1"/>
-    <row r="467" ht="14.25" customHeight="1"/>
-    <row r="468" ht="14.25" customHeight="1"/>
-    <row r="469" ht="14.25" customHeight="1"/>
-    <row r="470" ht="14.25" customHeight="1"/>
-    <row r="471" ht="14.25" customHeight="1"/>
-    <row r="472" ht="14.25" customHeight="1"/>
-    <row r="473" ht="14.25" customHeight="1"/>
-    <row r="474" ht="14.25" customHeight="1"/>
-    <row r="475" ht="14.25" customHeight="1"/>
-    <row r="476" ht="14.25" customHeight="1"/>
-    <row r="477" ht="14.25" customHeight="1"/>
-    <row r="478" ht="14.25" customHeight="1"/>
-    <row r="479" ht="14.25" customHeight="1"/>
-    <row r="480" ht="14.25" customHeight="1"/>
-    <row r="481" ht="14.25" customHeight="1"/>
-    <row r="482" ht="14.25" customHeight="1"/>
-    <row r="483" ht="14.25" customHeight="1"/>
-    <row r="484" ht="14.25" customHeight="1"/>
-    <row r="485" ht="14.25" customHeight="1"/>
-    <row r="486" ht="14.25" customHeight="1"/>
-    <row r="487" ht="14.25" customHeight="1"/>
-    <row r="488" ht="14.25" customHeight="1"/>
-    <row r="489" ht="14.25" customHeight="1"/>
-    <row r="490" ht="14.25" customHeight="1"/>
-    <row r="491" ht="14.25" customHeight="1"/>
-    <row r="492" ht="14.25" customHeight="1"/>
-    <row r="493" ht="14.25" customHeight="1"/>
-    <row r="494" ht="14.25" customHeight="1"/>
-    <row r="495" ht="14.25" customHeight="1"/>
-    <row r="496" ht="14.25" customHeight="1"/>
-    <row r="497" ht="14.25" customHeight="1"/>
-    <row r="498" ht="14.25" customHeight="1"/>
-    <row r="499" ht="14.25" customHeight="1"/>
-    <row r="500" ht="14.25" customHeight="1"/>
-    <row r="501" ht="14.25" customHeight="1"/>
-    <row r="502" ht="14.25" customHeight="1"/>
-    <row r="503" ht="14.25" customHeight="1"/>
-    <row r="504" ht="14.25" customHeight="1"/>
-    <row r="505" ht="14.25" customHeight="1"/>
-    <row r="506" ht="14.25" customHeight="1"/>
-    <row r="507" ht="14.25" customHeight="1"/>
-    <row r="508" ht="14.25" customHeight="1"/>
-    <row r="509" ht="14.25" customHeight="1"/>
-    <row r="510" ht="14.25" customHeight="1"/>
-    <row r="511" ht="14.25" customHeight="1"/>
-    <row r="512" ht="14.25" customHeight="1"/>
-    <row r="513" ht="14.25" customHeight="1"/>
-    <row r="514" ht="14.25" customHeight="1"/>
-    <row r="515" ht="14.25" customHeight="1"/>
-    <row r="516" ht="14.25" customHeight="1"/>
-    <row r="517" ht="14.25" customHeight="1"/>
-    <row r="518" ht="14.25" customHeight="1"/>
-    <row r="519" ht="14.25" customHeight="1"/>
-    <row r="520" ht="14.25" customHeight="1"/>
-    <row r="521" ht="14.25" customHeight="1"/>
-    <row r="522" ht="14.25" customHeight="1"/>
-    <row r="523" ht="14.25" customHeight="1"/>
-    <row r="524" ht="14.25" customHeight="1"/>
-    <row r="525" ht="14.25" customHeight="1"/>
-    <row r="526" ht="14.25" customHeight="1"/>
-    <row r="527" ht="14.25" customHeight="1"/>
-    <row r="528" ht="14.25" customHeight="1"/>
-    <row r="529" ht="14.25" customHeight="1"/>
-    <row r="530" ht="14.25" customHeight="1"/>
-    <row r="531" ht="14.25" customHeight="1"/>
-    <row r="532" ht="14.25" customHeight="1"/>
-    <row r="533" ht="14.25" customHeight="1"/>
-    <row r="534" ht="14.25" customHeight="1"/>
-    <row r="535" ht="14.25" customHeight="1"/>
-    <row r="536" ht="14.25" customHeight="1"/>
-    <row r="537" ht="14.25" customHeight="1"/>
-    <row r="538" ht="14.25" customHeight="1"/>
-    <row r="539" ht="14.25" customHeight="1"/>
-    <row r="540" ht="14.25" customHeight="1"/>
-    <row r="541" ht="14.25" customHeight="1"/>
-    <row r="542" ht="14.25" customHeight="1"/>
-    <row r="543" ht="14.25" customHeight="1"/>
-    <row r="544" ht="14.25" customHeight="1"/>
-    <row r="545" ht="14.25" customHeight="1"/>
-    <row r="546" ht="14.25" customHeight="1"/>
-    <row r="547" ht="14.25" customHeight="1"/>
-    <row r="548" ht="14.25" customHeight="1"/>
-    <row r="549" ht="14.25" customHeight="1"/>
-    <row r="550" ht="14.25" customHeight="1"/>
-    <row r="551" ht="14.25" customHeight="1"/>
-    <row r="552" ht="14.25" customHeight="1"/>
-    <row r="553" ht="14.25" customHeight="1"/>
-    <row r="554" ht="14.25" customHeight="1"/>
-    <row r="555" ht="14.25" customHeight="1"/>
-    <row r="556" ht="14.25" customHeight="1"/>
-    <row r="557" ht="14.25" customHeight="1"/>
-    <row r="558" ht="14.25" customHeight="1"/>
-    <row r="559" ht="14.25" customHeight="1"/>
-    <row r="560" ht="14.25" customHeight="1"/>
-    <row r="561" ht="14.25" customHeight="1"/>
-    <row r="562" ht="14.25" customHeight="1"/>
-    <row r="563" ht="14.25" customHeight="1"/>
-    <row r="564" ht="14.25" customHeight="1"/>
-    <row r="565" ht="14.25" customHeight="1"/>
-    <row r="566" ht="14.25" customHeight="1"/>
-    <row r="567" ht="14.25" customHeight="1"/>
-    <row r="568" ht="14.25" customHeight="1"/>
-    <row r="569" ht="14.25" customHeight="1"/>
-    <row r="570" ht="14.25" customHeight="1"/>
-    <row r="571" ht="14.25" customHeight="1"/>
-    <row r="572" ht="14.25" customHeight="1"/>
-    <row r="573" ht="14.25" customHeight="1"/>
-    <row r="574" ht="14.25" customHeight="1"/>
-    <row r="575" ht="14.25" customHeight="1"/>
-    <row r="576" ht="14.25" customHeight="1"/>
-    <row r="577" ht="14.25" customHeight="1"/>
-    <row r="578" ht="14.25" customHeight="1"/>
-    <row r="579" ht="14.25" customHeight="1"/>
-    <row r="580" ht="14.25" customHeight="1"/>
-    <row r="581" ht="14.25" customHeight="1"/>
-    <row r="582" ht="14.25" customHeight="1"/>
-    <row r="583" ht="14.25" customHeight="1"/>
-    <row r="584" ht="14.25" customHeight="1"/>
-    <row r="585" ht="14.25" customHeight="1"/>
-    <row r="586" ht="14.25" customHeight="1"/>
-    <row r="587" ht="14.25" customHeight="1"/>
-    <row r="588" ht="14.25" customHeight="1"/>
-    <row r="589" ht="14.25" customHeight="1"/>
-    <row r="590" ht="14.25" customHeight="1"/>
-    <row r="591" ht="14.25" customHeight="1"/>
-    <row r="592" ht="14.25" customHeight="1"/>
-    <row r="593" ht="14.25" customHeight="1"/>
-    <row r="594" ht="14.25" customHeight="1"/>
-    <row r="595" ht="14.25" customHeight="1"/>
-    <row r="596" ht="14.25" customHeight="1"/>
-    <row r="597" ht="14.25" customHeight="1"/>
-    <row r="598" ht="14.25" customHeight="1"/>
-    <row r="599" ht="14.25" customHeight="1"/>
-    <row r="600" ht="14.25" customHeight="1"/>
-    <row r="601" ht="14.25" customHeight="1"/>
-    <row r="602" ht="14.25" customHeight="1"/>
-    <row r="603" ht="14.25" customHeight="1"/>
-    <row r="604" ht="14.25" customHeight="1"/>
-    <row r="605" ht="14.25" customHeight="1"/>
-    <row r="606" ht="14.25" customHeight="1"/>
-    <row r="607" ht="14.25" customHeight="1"/>
-    <row r="608" ht="14.25" customHeight="1"/>
-    <row r="609" ht="14.25" customHeight="1"/>
-    <row r="610" ht="14.25" customHeight="1"/>
-    <row r="611" ht="14.25" customHeight="1"/>
-    <row r="612" ht="14.25" customHeight="1"/>
-    <row r="613" ht="14.25" customHeight="1"/>
-    <row r="614" ht="14.25" customHeight="1"/>
-    <row r="615" ht="14.25" customHeight="1"/>
-    <row r="616" ht="14.25" customHeight="1"/>
-    <row r="617" ht="14.25" customHeight="1"/>
-    <row r="618" ht="14.25" customHeight="1"/>
-    <row r="619" ht="14.25" customHeight="1"/>
-    <row r="620" ht="14.25" customHeight="1"/>
-    <row r="621" ht="14.25" customHeight="1"/>
-    <row r="622" ht="14.25" customHeight="1"/>
-    <row r="623" ht="14.25" customHeight="1"/>
-    <row r="624" ht="14.25" customHeight="1"/>
-    <row r="625" ht="14.25" customHeight="1"/>
-    <row r="626" ht="14.25" customHeight="1"/>
-    <row r="627" ht="14.25" customHeight="1"/>
-    <row r="628" ht="14.25" customHeight="1"/>
-    <row r="629" ht="14.25" customHeight="1"/>
-    <row r="630" ht="14.25" customHeight="1"/>
-    <row r="631" ht="14.25" customHeight="1"/>
-    <row r="632" ht="14.25" customHeight="1"/>
-    <row r="633" ht="14.25" customHeight="1"/>
-    <row r="634" ht="14.25" customHeight="1"/>
-    <row r="635" ht="14.25" customHeight="1"/>
-    <row r="636" ht="14.25" customHeight="1"/>
-    <row r="637" ht="14.25" customHeight="1"/>
-    <row r="638" ht="14.25" customHeight="1"/>
-    <row r="639" ht="14.25" customHeight="1"/>
-    <row r="640" ht="14.25" customHeight="1"/>
-    <row r="641" ht="14.25" customHeight="1"/>
-    <row r="642" ht="14.25" customHeight="1"/>
-    <row r="643" ht="14.25" customHeight="1"/>
-    <row r="644" ht="14.25" customHeight="1"/>
-    <row r="645" ht="14.25" customHeight="1"/>
-    <row r="646" ht="14.25" customHeight="1"/>
-    <row r="647" ht="14.25" customHeight="1"/>
-    <row r="648" ht="14.25" customHeight="1"/>
-    <row r="649" ht="14.25" customHeight="1"/>
-    <row r="650" ht="14.25" customHeight="1"/>
-    <row r="651" ht="14.25" customHeight="1"/>
-    <row r="652" ht="14.25" customHeight="1"/>
-    <row r="653" ht="14.25" customHeight="1"/>
-    <row r="654" ht="14.25" customHeight="1"/>
-    <row r="655" ht="14.25" customHeight="1"/>
-    <row r="656" ht="14.25" customHeight="1"/>
-    <row r="657" ht="14.25" customHeight="1"/>
-    <row r="658" ht="14.25" customHeight="1"/>
-    <row r="659" ht="14.25" customHeight="1"/>
-    <row r="660" ht="14.25" customHeight="1"/>
-    <row r="661" ht="14.25" customHeight="1"/>
-    <row r="662" ht="14.25" customHeight="1"/>
-    <row r="663" ht="14.25" customHeight="1"/>
-    <row r="664" ht="14.25" customHeight="1"/>
-    <row r="665" ht="14.25" customHeight="1"/>
-    <row r="666" ht="14.25" customHeight="1"/>
-    <row r="667" ht="14.25" customHeight="1"/>
-    <row r="668" ht="14.25" customHeight="1"/>
-    <row r="669" ht="14.25" customHeight="1"/>
-    <row r="670" ht="14.25" customHeight="1"/>
-    <row r="671" ht="14.25" customHeight="1"/>
-    <row r="672" ht="14.25" customHeight="1"/>
-    <row r="673" ht="14.25" customHeight="1"/>
-    <row r="674" ht="14.25" customHeight="1"/>
-    <row r="675" ht="14.25" customHeight="1"/>
-    <row r="676" ht="14.25" customHeight="1"/>
-    <row r="677" ht="14.25" customHeight="1"/>
-    <row r="678" ht="14.25" customHeight="1"/>
-    <row r="679" ht="14.25" customHeight="1"/>
-    <row r="680" ht="14.25" customHeight="1"/>
-    <row r="681" ht="14.25" customHeight="1"/>
-    <row r="682" ht="14.25" customHeight="1"/>
-    <row r="683" ht="14.25" customHeight="1"/>
-    <row r="684" ht="14.25" customHeight="1"/>
-    <row r="685" ht="14.25" customHeight="1"/>
-    <row r="686" ht="14.25" customHeight="1"/>
-    <row r="687" ht="14.25" customHeight="1"/>
-    <row r="688" ht="14.25" customHeight="1"/>
-    <row r="689" ht="14.25" customHeight="1"/>
-    <row r="690" ht="14.25" customHeight="1"/>
-    <row r="691" ht="14.25" customHeight="1"/>
-    <row r="692" ht="14.25" customHeight="1"/>
-    <row r="693" ht="14.25" customHeight="1"/>
-    <row r="694" ht="14.25" customHeight="1"/>
-    <row r="695" ht="14.25" customHeight="1"/>
-    <row r="696" ht="14.25" customHeight="1"/>
-    <row r="697" ht="14.25" customHeight="1"/>
-    <row r="698" ht="14.25" customHeight="1"/>
-    <row r="699" ht="14.25" customHeight="1"/>
-    <row r="700" ht="14.25" customHeight="1"/>
-    <row r="701" ht="14.25" customHeight="1"/>
-    <row r="702" ht="14.25" customHeight="1"/>
-    <row r="703" ht="14.25" customHeight="1"/>
-    <row r="704" ht="14.25" customHeight="1"/>
-    <row r="705" ht="14.25" customHeight="1"/>
-    <row r="706" ht="14.25" customHeight="1"/>
-    <row r="707" ht="14.25" customHeight="1"/>
-    <row r="708" ht="14.25" customHeight="1"/>
-    <row r="709" ht="14.25" customHeight="1"/>
-    <row r="710" ht="14.25" customHeight="1"/>
-    <row r="711" ht="14.25" customHeight="1"/>
-    <row r="712" ht="14.25" customHeight="1"/>
-    <row r="713" ht="14.25" customHeight="1"/>
-    <row r="714" ht="14.25" customHeight="1"/>
-    <row r="715" ht="14.25" customHeight="1"/>
-    <row r="716" ht="14.25" customHeight="1"/>
-    <row r="717" ht="14.25" customHeight="1"/>
-    <row r="718" ht="14.25" customHeight="1"/>
-    <row r="719" ht="14.25" customHeight="1"/>
-    <row r="720" ht="14.25" customHeight="1"/>
-    <row r="721" ht="14.25" customHeight="1"/>
-    <row r="722" ht="14.25" customHeight="1"/>
-    <row r="723" ht="14.25" customHeight="1"/>
-    <row r="724" ht="14.25" customHeight="1"/>
-    <row r="725" ht="14.25" customHeight="1"/>
-    <row r="726" ht="14.25" customHeight="1"/>
-    <row r="727" ht="14.25" customHeight="1"/>
-    <row r="728" ht="14.25" customHeight="1"/>
-    <row r="729" ht="14.25" customHeight="1"/>
-    <row r="730" ht="14.25" customHeight="1"/>
-    <row r="731" ht="14.25" customHeight="1"/>
-    <row r="732" ht="14.25" customHeight="1"/>
-    <row r="733" ht="14.25" customHeight="1"/>
-    <row r="734" ht="14.25" customHeight="1"/>
-    <row r="735" ht="14.25" customHeight="1"/>
-    <row r="736" ht="14.25" customHeight="1"/>
-    <row r="737" ht="14.25" customHeight="1"/>
-    <row r="738" ht="14.25" customHeight="1"/>
-    <row r="739" ht="14.25" customHeight="1"/>
-    <row r="740" ht="14.25" customHeight="1"/>
-    <row r="741" ht="14.25" customHeight="1"/>
-    <row r="742" ht="14.25" customHeight="1"/>
-    <row r="743" ht="14.25" customHeight="1"/>
-    <row r="744" ht="14.25" customHeight="1"/>
-    <row r="745" ht="14.25" customHeight="1"/>
-    <row r="746" ht="14.25" customHeight="1"/>
-    <row r="747" ht="14.25" customHeight="1"/>
-    <row r="748" ht="14.25" customHeight="1"/>
-    <row r="749" ht="14.25" customHeight="1"/>
-    <row r="750" ht="14.25" customHeight="1"/>
-    <row r="751" ht="14.25" customHeight="1"/>
-    <row r="752" ht="14.25" customHeight="1"/>
-    <row r="753" ht="14.25" customHeight="1"/>
-    <row r="754" ht="14.25" customHeight="1"/>
-    <row r="755" ht="14.25" customHeight="1"/>
-    <row r="756" ht="14.25" customHeight="1"/>
-    <row r="757" ht="14.25" customHeight="1"/>
-    <row r="758" ht="14.25" customHeight="1"/>
-    <row r="759" ht="14.25" customHeight="1"/>
-    <row r="760" ht="14.25" customHeight="1"/>
-    <row r="761" ht="14.25" customHeight="1"/>
-    <row r="762" ht="14.25" customHeight="1"/>
-    <row r="763" ht="14.25" customHeight="1"/>
-    <row r="764" ht="14.25" customHeight="1"/>
-    <row r="765" ht="14.25" customHeight="1"/>
-    <row r="766" ht="14.25" customHeight="1"/>
-    <row r="767" ht="14.25" customHeight="1"/>
-    <row r="768" ht="14.25" customHeight="1"/>
-    <row r="769" ht="14.25" customHeight="1"/>
-    <row r="770" ht="14.25" customHeight="1"/>
-    <row r="771" ht="14.25" customHeight="1"/>
-    <row r="772" ht="14.25" customHeight="1"/>
-    <row r="773" ht="14.25" customHeight="1"/>
-    <row r="774" ht="14.25" customHeight="1"/>
-    <row r="775" ht="14.25" customHeight="1"/>
-    <row r="776" ht="14.25" customHeight="1"/>
-    <row r="777" ht="14.25" customHeight="1"/>
-    <row r="778" ht="14.25" customHeight="1"/>
-    <row r="779" ht="14.25" customHeight="1"/>
-    <row r="780" ht="14.25" customHeight="1"/>
-    <row r="781" ht="14.25" customHeight="1"/>
-    <row r="782" ht="14.25" customHeight="1"/>
-    <row r="783" ht="14.25" customHeight="1"/>
-    <row r="784" ht="14.25" customHeight="1"/>
-    <row r="785" ht="14.25" customHeight="1"/>
-    <row r="786" ht="14.25" customHeight="1"/>
-    <row r="787" ht="14.25" customHeight="1"/>
-    <row r="788" ht="14.25" customHeight="1"/>
-    <row r="789" ht="14.25" customHeight="1"/>
-    <row r="790" ht="14.25" customHeight="1"/>
-    <row r="791" ht="14.25" customHeight="1"/>
-    <row r="792" ht="14.25" customHeight="1"/>
-    <row r="793" ht="14.25" customHeight="1"/>
-    <row r="794" ht="14.25" customHeight="1"/>
-    <row r="795" ht="14.25" customHeight="1"/>
-    <row r="796" ht="14.25" customHeight="1"/>
-    <row r="797" ht="14.25" customHeight="1"/>
-    <row r="798" ht="14.25" customHeight="1"/>
-    <row r="799" ht="14.25" customHeight="1"/>
-    <row r="800" ht="14.25" customHeight="1"/>
-    <row r="801" ht="14.25" customHeight="1"/>
-    <row r="802" ht="14.25" customHeight="1"/>
-    <row r="803" ht="14.25" customHeight="1"/>
-    <row r="804" ht="14.25" customHeight="1"/>
-    <row r="805" ht="14.25" customHeight="1"/>
-    <row r="806" ht="14.25" customHeight="1"/>
-    <row r="807" ht="14.25" customHeight="1"/>
-    <row r="808" ht="14.25" customHeight="1"/>
-    <row r="809" ht="14.25" customHeight="1"/>
-    <row r="810" ht="14.25" customHeight="1"/>
-    <row r="811" ht="14.25" customHeight="1"/>
-    <row r="812" ht="14.25" customHeight="1"/>
-    <row r="813" ht="14.25" customHeight="1"/>
-    <row r="814" ht="14.25" customHeight="1"/>
-    <row r="815" ht="14.25" customHeight="1"/>
-    <row r="816" ht="14.25" customHeight="1"/>
-    <row r="817" ht="14.25" customHeight="1"/>
-    <row r="818" ht="14.25" customHeight="1"/>
-    <row r="819" ht="14.25" customHeight="1"/>
-    <row r="820" ht="14.25" customHeight="1"/>
-    <row r="821" ht="14.25" customHeight="1"/>
-    <row r="822" ht="14.25" customHeight="1"/>
-    <row r="823" ht="14.25" customHeight="1"/>
-    <row r="824" ht="14.25" customHeight="1"/>
-    <row r="825" ht="14.25" customHeight="1"/>
-    <row r="826" ht="14.25" customHeight="1"/>
-    <row r="827" ht="14.25" customHeight="1"/>
-    <row r="828" ht="14.25" customHeight="1"/>
-    <row r="829" ht="14.25" customHeight="1"/>
-    <row r="830" ht="14.25" customHeight="1"/>
-    <row r="831" ht="14.25" customHeight="1"/>
-    <row r="832" ht="14.25" customHeight="1"/>
-    <row r="833" ht="14.25" customHeight="1"/>
-    <row r="834" ht="14.25" customHeight="1"/>
-    <row r="835" ht="14.25" customHeight="1"/>
-    <row r="836" ht="14.25" customHeight="1"/>
-    <row r="837" ht="14.25" customHeight="1"/>
-    <row r="838" ht="14.25" customHeight="1"/>
-    <row r="839" ht="14.25" customHeight="1"/>
-    <row r="840" ht="14.25" customHeight="1"/>
-    <row r="841" ht="14.25" customHeight="1"/>
-    <row r="842" ht="14.25" customHeight="1"/>
-    <row r="843" ht="14.25" customHeight="1"/>
-    <row r="844" ht="14.25" customHeight="1"/>
-    <row r="845" ht="14.25" customHeight="1"/>
-    <row r="846" ht="14.25" customHeight="1"/>
-    <row r="847" ht="14.25" customHeight="1"/>
-    <row r="848" ht="14.25" customHeight="1"/>
-    <row r="849" ht="14.25" customHeight="1"/>
-    <row r="850" ht="14.25" customHeight="1"/>
-    <row r="851" ht="14.25" customHeight="1"/>
-    <row r="852" ht="14.25" customHeight="1"/>
-    <row r="853" ht="14.25" customHeight="1"/>
-    <row r="854" ht="14.25" customHeight="1"/>
-    <row r="855" ht="14.25" customHeight="1"/>
-    <row r="856" ht="14.25" customHeight="1"/>
-    <row r="857" ht="14.25" customHeight="1"/>
-    <row r="858" ht="14.25" customHeight="1"/>
-    <row r="859" ht="14.25" customHeight="1"/>
-    <row r="860" ht="14.25" customHeight="1"/>
-    <row r="861" ht="14.25" customHeight="1"/>
-    <row r="862" ht="14.25" customHeight="1"/>
-    <row r="863" ht="14.25" customHeight="1"/>
-    <row r="864" ht="14.25" customHeight="1"/>
-    <row r="865" ht="14.25" customHeight="1"/>
-    <row r="866" ht="14.25" customHeight="1"/>
-    <row r="867" ht="14.25" customHeight="1"/>
-    <row r="868" ht="14.25" customHeight="1"/>
-    <row r="869" ht="14.25" customHeight="1"/>
-    <row r="870" ht="14.25" customHeight="1"/>
-    <row r="871" ht="14.25" customHeight="1"/>
-    <row r="872" ht="14.25" customHeight="1"/>
-    <row r="873" ht="14.25" customHeight="1"/>
-    <row r="874" ht="14.25" customHeight="1"/>
-    <row r="875" ht="14.25" customHeight="1"/>
-    <row r="876" ht="14.25" customHeight="1"/>
-    <row r="877" ht="14.25" customHeight="1"/>
-    <row r="878" ht="14.25" customHeight="1"/>
-    <row r="879" ht="14.25" customHeight="1"/>
-    <row r="880" ht="14.25" customHeight="1"/>
-    <row r="881" ht="14.25" customHeight="1"/>
-    <row r="882" ht="14.25" customHeight="1"/>
-    <row r="883" ht="14.25" customHeight="1"/>
-    <row r="884" ht="14.25" customHeight="1"/>
-    <row r="885" ht="14.25" customHeight="1"/>
-    <row r="886" ht="14.25" customHeight="1"/>
-    <row r="887" ht="14.25" customHeight="1"/>
-    <row r="888" ht="14.25" customHeight="1"/>
-    <row r="889" ht="14.25" customHeight="1"/>
-    <row r="890" ht="14.25" customHeight="1"/>
-    <row r="891" ht="14.25" customHeight="1"/>
-    <row r="892" ht="14.25" customHeight="1"/>
-    <row r="893" ht="14.25" customHeight="1"/>
-    <row r="894" ht="14.25" customHeight="1"/>
-    <row r="895" ht="14.25" customHeight="1"/>
-    <row r="896" ht="14.25" customHeight="1"/>
-    <row r="897" ht="14.25" customHeight="1"/>
-    <row r="898" ht="14.25" customHeight="1"/>
-    <row r="899" ht="14.25" customHeight="1"/>
-    <row r="900" ht="14.25" customHeight="1"/>
-    <row r="901" ht="14.25" customHeight="1"/>
-    <row r="902" ht="14.25" customHeight="1"/>
-    <row r="903" ht="14.25" customHeight="1"/>
-    <row r="904" ht="14.25" customHeight="1"/>
-    <row r="905" ht="14.25" customHeight="1"/>
-    <row r="906" ht="14.25" customHeight="1"/>
-    <row r="907" ht="14.25" customHeight="1"/>
-    <row r="908" ht="14.25" customHeight="1"/>
-    <row r="909" ht="14.25" customHeight="1"/>
-    <row r="910" ht="14.25" customHeight="1"/>
-    <row r="911" ht="14.25" customHeight="1"/>
-    <row r="912" ht="14.25" customHeight="1"/>
-    <row r="913" ht="14.25" customHeight="1"/>
-    <row r="914" ht="14.25" customHeight="1"/>
-    <row r="915" ht="14.25" customHeight="1"/>
-    <row r="916" ht="14.25" customHeight="1"/>
-    <row r="917" ht="14.25" customHeight="1"/>
-    <row r="918" ht="14.25" customHeight="1"/>
-    <row r="919" ht="14.25" customHeight="1"/>
-    <row r="920" ht="14.25" customHeight="1"/>
-    <row r="921" ht="14.25" customHeight="1"/>
-    <row r="922" ht="14.25" customHeight="1"/>
-    <row r="923" ht="14.25" customHeight="1"/>
-    <row r="924" ht="14.25" customHeight="1"/>
-    <row r="925" ht="14.25" customHeight="1"/>
-    <row r="926" ht="14.25" customHeight="1"/>
-    <row r="927" ht="14.25" customHeight="1"/>
-    <row r="928" ht="14.25" customHeight="1"/>
-    <row r="929" ht="14.25" customHeight="1"/>
-    <row r="930" ht="14.25" customHeight="1"/>
-    <row r="931" ht="14.25" customHeight="1"/>
-    <row r="932" ht="14.25" customHeight="1"/>
-    <row r="933" ht="14.25" customHeight="1"/>
-    <row r="934" ht="14.25" customHeight="1"/>
-    <row r="935" ht="14.25" customHeight="1"/>
-    <row r="936" ht="14.25" customHeight="1"/>
-    <row r="937" ht="14.25" customHeight="1"/>
-    <row r="938" ht="14.25" customHeight="1"/>
-    <row r="939" ht="14.25" customHeight="1"/>
-    <row r="940" ht="14.25" customHeight="1"/>
-    <row r="941" ht="14.25" customHeight="1"/>
-    <row r="942" ht="14.25" customHeight="1"/>
-    <row r="943" ht="14.25" customHeight="1"/>
-    <row r="944" ht="14.25" customHeight="1"/>
-    <row r="945" ht="14.25" customHeight="1"/>
-    <row r="946" ht="14.25" customHeight="1"/>
-    <row r="947" ht="14.25" customHeight="1"/>
-    <row r="948" ht="14.25" customHeight="1"/>
-    <row r="949" ht="14.25" customHeight="1"/>
-    <row r="950" ht="14.25" customHeight="1"/>
-    <row r="951" ht="14.25" customHeight="1"/>
-    <row r="952" ht="14.25" customHeight="1"/>
-    <row r="953" ht="14.25" customHeight="1"/>
-    <row r="954" ht="14.25" customHeight="1"/>
-    <row r="955" ht="14.25" customHeight="1"/>
-    <row r="956" ht="14.25" customHeight="1"/>
-    <row r="957" ht="14.25" customHeight="1"/>
-    <row r="958" ht="14.25" customHeight="1"/>
-    <row r="959" ht="14.25" customHeight="1"/>
-    <row r="960" ht="14.25" customHeight="1"/>
-    <row r="961" ht="14.25" customHeight="1"/>
-    <row r="962" ht="14.25" customHeight="1"/>
-    <row r="963" ht="14.25" customHeight="1"/>
-    <row r="964" ht="14.25" customHeight="1"/>
-    <row r="965" ht="14.25" customHeight="1"/>
-    <row r="966" ht="14.25" customHeight="1"/>
-    <row r="967" ht="14.25" customHeight="1"/>
-    <row r="968" ht="14.25" customHeight="1"/>
-    <row r="969" ht="14.25" customHeight="1"/>
-    <row r="970" ht="14.25" customHeight="1"/>
-    <row r="971" ht="14.25" customHeight="1"/>
-    <row r="972" ht="14.25" customHeight="1"/>
-    <row r="973" ht="14.25" customHeight="1"/>
-    <row r="974" ht="14.25" customHeight="1"/>
-    <row r="975" ht="14.25" customHeight="1"/>
-    <row r="976" ht="14.25" customHeight="1"/>
-    <row r="977" ht="14.25" customHeight="1"/>
-    <row r="978" ht="14.25" customHeight="1"/>
-    <row r="979" ht="14.25" customHeight="1"/>
-    <row r="980" ht="14.25" customHeight="1"/>
-    <row r="981" ht="14.25" customHeight="1"/>
-    <row r="982" ht="14.25" customHeight="1"/>
-    <row r="983" ht="14.25" customHeight="1"/>
-    <row r="984" ht="14.25" customHeight="1"/>
-    <row r="985" ht="14.25" customHeight="1"/>
-    <row r="986" ht="14.25" customHeight="1"/>
-    <row r="987" ht="14.25" customHeight="1"/>
-    <row r="988" ht="14.25" customHeight="1"/>
-    <row r="989" ht="14.25" customHeight="1"/>
-    <row r="990" ht="14.25" customHeight="1"/>
-    <row r="991" ht="14.25" customHeight="1"/>
-    <row r="992" ht="14.25" customHeight="1"/>
-    <row r="993" ht="14.25" customHeight="1"/>
-    <row r="994" ht="14.25" customHeight="1"/>
-    <row r="995" ht="14.25" customHeight="1"/>
-    <row r="996" ht="14.25" customHeight="1"/>
-    <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
+    <row r="173" spans="2:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" spans="2:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" spans="2:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" spans="2:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:A59"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>149</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:AA85"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>317</v>
       </c>
@@ -7357,7 +7985,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
@@ -7368,10 +7996,10 @@
         <v>14</v>
       </c>
       <c r="D2" s="7">
-        <v>-32.7032</v>
+        <v>-32.703200000000002</v>
       </c>
       <c r="E2" s="7">
-        <v>18.2203</v>
+        <v>18.220300000000002</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
@@ -7396,7 +8024,7 @@
       <c r="Z2" s="9"/>
       <c r="AA2" s="9"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>18</v>
       </c>
@@ -7407,10 +8035,10 @@
         <v>19</v>
       </c>
       <c r="D3" s="7">
-        <v>-32.7032</v>
+        <v>-32.703200000000002</v>
       </c>
       <c r="E3" s="7">
-        <v>18.2203</v>
+        <v>18.220300000000002</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
@@ -7435,7 +8063,7 @@
       <c r="Z3" s="9"/>
       <c r="AA3" s="9"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>20</v>
       </c>
@@ -7446,10 +8074,10 @@
         <v>21</v>
       </c>
       <c r="D4" s="7">
-        <v>-32.7032</v>
+        <v>-32.703200000000002</v>
       </c>
       <c r="E4" s="7">
-        <v>18.2203</v>
+        <v>18.220300000000002</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
@@ -7474,7 +8102,7 @@
       <c r="Z4" s="9"/>
       <c r="AA4" s="9"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>22</v>
       </c>
@@ -7485,7 +8113,7 @@
         <v>24</v>
       </c>
       <c r="D5" s="7">
-        <v>-32.8096</v>
+        <v>-32.809600000000003</v>
       </c>
       <c r="E5" s="7">
         <v>17.89104</v>
@@ -7513,7 +8141,7 @@
       <c r="Z5" s="9"/>
       <c r="AA5" s="9"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>25</v>
       </c>
@@ -7524,7 +8152,7 @@
         <v>26</v>
       </c>
       <c r="D6" s="7">
-        <v>-32.8096</v>
+        <v>-32.809600000000003</v>
       </c>
       <c r="E6" s="7">
         <v>17.89104</v>
@@ -7552,7 +8180,7 @@
       <c r="Z6" s="9"/>
       <c r="AA6" s="9"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>27</v>
       </c>
@@ -7563,7 +8191,7 @@
         <v>28</v>
       </c>
       <c r="D7" s="7">
-        <v>-32.8096</v>
+        <v>-32.809600000000003</v>
       </c>
       <c r="E7" s="7">
         <v>17.89104</v>
@@ -7591,7 +8219,7 @@
       <c r="Z7" s="9"/>
       <c r="AA7" s="9"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>107</v>
       </c>
@@ -7602,10 +8230,10 @@
         <v>158</v>
       </c>
       <c r="D8" s="7">
-        <v>28.35639</v>
+        <v>28.356390000000001</v>
       </c>
       <c r="E8" s="7">
-        <v>-14.0339</v>
+        <v>-14.033899999999999</v>
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
@@ -7630,7 +8258,7 @@
       <c r="Z8" s="9"/>
       <c r="AA8" s="9"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>34</v>
       </c>
@@ -7641,10 +8269,10 @@
         <v>161</v>
       </c>
       <c r="D9" s="7">
-        <v>35.1264</v>
+        <v>35.126399999999997</v>
       </c>
       <c r="E9" s="7">
-        <v>33.4299</v>
+        <v>33.429900000000004</v>
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
@@ -7669,7 +8297,7 @@
       <c r="Z9" s="9"/>
       <c r="AA9" s="9"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>162</v>
       </c>
@@ -7680,10 +8308,10 @@
         <v>163</v>
       </c>
       <c r="D10" s="7">
-        <v>35.1264</v>
+        <v>35.126399999999997</v>
       </c>
       <c r="E10" s="7">
-        <v>33.4299</v>
+        <v>33.429900000000004</v>
       </c>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
@@ -7708,7 +8336,7 @@
       <c r="Z10" s="9"/>
       <c r="AA10" s="9"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>97</v>
       </c>
@@ -7719,7 +8347,7 @@
         <v>167</v>
       </c>
       <c r="D11" s="7">
-        <v>31.35611</v>
+        <v>31.356110000000001</v>
       </c>
       <c r="E11" s="7">
         <v>27.2075</v>
@@ -7747,7 +8375,7 @@
       <c r="Z11" s="9"/>
       <c r="AA11" s="9"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>133</v>
       </c>
@@ -7758,10 +8386,10 @@
         <v>168</v>
       </c>
       <c r="D12" s="7">
-        <v>31.2675</v>
+        <v>31.267499999999998</v>
       </c>
       <c r="E12" s="7">
-        <v>30.17861</v>
+        <v>30.178609999999999</v>
       </c>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
@@ -7786,7 +8414,7 @@
       <c r="Z12" s="9"/>
       <c r="AA12" s="9"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>45</v>
       </c>
@@ -7797,10 +8425,10 @@
         <v>169</v>
       </c>
       <c r="D13" s="7">
-        <v>31.2675</v>
+        <v>31.267499999999998</v>
       </c>
       <c r="E13" s="7">
-        <v>30.17861</v>
+        <v>30.178609999999999</v>
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
@@ -7825,7 +8453,7 @@
       <c r="Z13" s="9"/>
       <c r="AA13" s="9"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>60</v>
       </c>
@@ -7836,7 +8464,7 @@
         <v>170</v>
       </c>
       <c r="D14" s="7">
-        <v>31.35611</v>
+        <v>31.356110000000001</v>
       </c>
       <c r="E14" s="7">
         <v>27.2075</v>
@@ -7864,7 +8492,7 @@
       <c r="Z14" s="9"/>
       <c r="AA14" s="9"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>171</v>
       </c>
@@ -7875,7 +8503,7 @@
         <v>172</v>
       </c>
       <c r="D15" s="7">
-        <v>31.35611</v>
+        <v>31.356110000000001</v>
       </c>
       <c r="E15" s="7">
         <v>27.2075</v>
@@ -7903,7 +8531,7 @@
       <c r="Z15" s="9"/>
       <c r="AA15" s="9"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>69</v>
       </c>
@@ -7914,10 +8542,10 @@
         <v>173</v>
       </c>
       <c r="D16" s="7">
-        <v>31.2675</v>
+        <v>31.267499999999998</v>
       </c>
       <c r="E16" s="7">
-        <v>30.17861</v>
+        <v>30.178609999999999</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
@@ -7942,7 +8570,7 @@
       <c r="Z16" s="9"/>
       <c r="AA16" s="9"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>100</v>
       </c>
@@ -7953,10 +8581,10 @@
         <v>174</v>
       </c>
       <c r="D17" s="7">
-        <v>31.2675</v>
+        <v>31.267499999999998</v>
       </c>
       <c r="E17" s="7">
-        <v>30.17861</v>
+        <v>30.178609999999999</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
@@ -7981,7 +8609,7 @@
       <c r="Z17" s="9"/>
       <c r="AA17" s="9"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>130</v>
       </c>
@@ -7992,10 +8620,10 @@
         <v>176</v>
       </c>
       <c r="D18" s="7">
-        <v>37.97667</v>
+        <v>37.976669999999999</v>
       </c>
       <c r="E18" s="7">
-        <v>12.49556</v>
+        <v>12.495559999999999</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
@@ -8020,7 +8648,7 @@
       <c r="Z18" s="9"/>
       <c r="AA18" s="9"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>177</v>
       </c>
@@ -8031,10 +8659,10 @@
         <v>178</v>
       </c>
       <c r="D19" s="7">
-        <v>37.97667</v>
+        <v>37.976669999999999</v>
       </c>
       <c r="E19" s="7">
-        <v>12.49556</v>
+        <v>12.495559999999999</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
@@ -8059,7 +8687,7 @@
       <c r="Z19" s="9"/>
       <c r="AA19" s="9"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>179</v>
       </c>
@@ -8070,10 +8698,10 @@
         <v>180</v>
       </c>
       <c r="D20" s="7">
-        <v>37.97667</v>
+        <v>37.976669999999999</v>
       </c>
       <c r="E20" s="7">
-        <v>12.49556</v>
+        <v>12.495559999999999</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
@@ -8098,7 +8726,7 @@
       <c r="Z20" s="9"/>
       <c r="AA20" s="9"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>36</v>
       </c>
@@ -8109,10 +8737,10 @@
         <v>181</v>
       </c>
       <c r="D21" s="7">
-        <v>37.97667</v>
+        <v>37.976669999999999</v>
       </c>
       <c r="E21" s="7">
-        <v>12.49556</v>
+        <v>12.495559999999999</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
@@ -8137,7 +8765,7 @@
       <c r="Z21" s="9"/>
       <c r="AA21" s="9"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>55</v>
       </c>
@@ -8148,10 +8776,10 @@
         <v>182</v>
       </c>
       <c r="D22" s="7">
-        <v>35.50167</v>
+        <v>35.501669999999997</v>
       </c>
       <c r="E22" s="7">
-        <v>12.60278</v>
+        <v>12.602779999999999</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
@@ -8176,7 +8804,7 @@
       <c r="Z22" s="9"/>
       <c r="AA22" s="9"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>95</v>
       </c>
@@ -8187,10 +8815,10 @@
         <v>185</v>
       </c>
       <c r="D23" s="7">
-        <v>27.29801</v>
+        <v>27.298010000000001</v>
       </c>
       <c r="E23" s="7">
-        <v>-112.906</v>
+        <v>-112.90600000000001</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
@@ -8215,7 +8843,7 @@
       <c r="Z23" s="9"/>
       <c r="AA23" s="9"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>126</v>
       </c>
@@ -8226,10 +8854,10 @@
         <v>188</v>
       </c>
       <c r="D24" s="7">
-        <v>27.67047</v>
+        <v>27.670470000000002</v>
       </c>
       <c r="E24" s="7">
-        <v>-114.653</v>
+        <v>-114.65300000000001</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
@@ -8254,7 +8882,7 @@
       <c r="Z24" s="9"/>
       <c r="AA24" s="9"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>189</v>
       </c>
@@ -8265,7 +8893,7 @@
         <v>190</v>
       </c>
       <c r="D25" s="7">
-        <v>30.48589</v>
+        <v>30.485890000000001</v>
       </c>
       <c r="E25" s="7">
         <v>-116.105</v>
@@ -8293,7 +8921,7 @@
       <c r="Z25" s="9"/>
       <c r="AA25" s="9"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>140</v>
       </c>
@@ -8304,7 +8932,7 @@
         <v>200</v>
       </c>
       <c r="D26" s="7">
-        <v>32.41229</v>
+        <v>32.412289999999999</v>
       </c>
       <c r="E26" s="7">
         <v>-117.245</v>
@@ -8332,7 +8960,7 @@
       <c r="Z26" s="9"/>
       <c r="AA26" s="9"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>201</v>
       </c>
@@ -8343,10 +8971,10 @@
         <v>202</v>
       </c>
       <c r="D27" s="7">
-        <v>32.40162</v>
+        <v>32.401620000000001</v>
       </c>
       <c r="E27" s="7">
-        <v>-117.243</v>
+        <v>-117.24299999999999</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
@@ -8371,7 +8999,7 @@
       <c r="Z27" s="9"/>
       <c r="AA27" s="9"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>135</v>
       </c>
@@ -8382,7 +9010,7 @@
         <v>203</v>
       </c>
       <c r="D28" s="7">
-        <v>34.38721</v>
+        <v>34.387210000000003</v>
       </c>
       <c r="E28" s="7">
         <v>-119.512</v>
@@ -8410,7 +9038,7 @@
       <c r="Z28" s="9"/>
       <c r="AA28" s="9"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>119</v>
       </c>
@@ -8449,7 +9077,7 @@
       <c r="Z29" s="9"/>
       <c r="AA29" s="9"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>205</v>
       </c>
@@ -8460,7 +9088,7 @@
         <v>206</v>
       </c>
       <c r="D30" s="7">
-        <v>34.38707</v>
+        <v>34.387070000000001</v>
       </c>
       <c r="E30" s="7">
         <v>-119.511</v>
@@ -8488,7 +9116,7 @@
       <c r="Z30" s="9"/>
       <c r="AA30" s="9"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>207</v>
       </c>
@@ -8499,10 +9127,10 @@
         <v>208</v>
       </c>
       <c r="D31" s="7">
-        <v>36.51207</v>
+        <v>36.512070000000001</v>
       </c>
       <c r="E31" s="7">
-        <v>-121.942</v>
+        <v>-121.94199999999999</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
@@ -8527,7 +9155,7 @@
       <c r="Z31" s="9"/>
       <c r="AA31" s="9"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>115</v>
       </c>
@@ -8538,7 +9166,7 @@
         <v>209</v>
       </c>
       <c r="D32" s="7">
-        <v>34.38737</v>
+        <v>34.387369999999997</v>
       </c>
       <c r="E32" s="7">
         <v>-119.512</v>
@@ -8566,7 +9194,7 @@
       <c r="Z32" s="9"/>
       <c r="AA32" s="9"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>58</v>
       </c>
@@ -8577,10 +9205,10 @@
         <v>210</v>
       </c>
       <c r="D33" s="7">
-        <v>34.01528</v>
+        <v>34.015279999999997</v>
       </c>
       <c r="E33" s="7">
-        <v>-119.362</v>
+        <v>-119.36199999999999</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
@@ -8605,7 +9233,7 @@
       <c r="Z33" s="9"/>
       <c r="AA33" s="9"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>41</v>
       </c>
@@ -8616,7 +9244,7 @@
         <v>211</v>
       </c>
       <c r="D34" s="7">
-        <v>34.01583</v>
+        <v>34.015830000000001</v>
       </c>
       <c r="E34" s="7">
         <v>-119.36</v>
@@ -8644,7 +9272,7 @@
       <c r="Z34" s="9"/>
       <c r="AA34" s="9"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>212</v>
       </c>
@@ -8655,10 +9283,10 @@
         <v>213</v>
       </c>
       <c r="D35" s="7">
-        <v>34.01528</v>
+        <v>34.015279999999997</v>
       </c>
       <c r="E35" s="7">
-        <v>-119.362</v>
+        <v>-119.36199999999999</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
@@ -8683,7 +9311,7 @@
       <c r="Z35" s="9"/>
       <c r="AA35" s="9"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>164</v>
       </c>
@@ -8694,7 +9322,7 @@
         <v>214</v>
       </c>
       <c r="D36" s="7">
-        <v>34.01556</v>
+        <v>34.015560000000001</v>
       </c>
       <c r="E36" s="7">
         <v>-119.361</v>
@@ -8722,7 +9350,7 @@
       <c r="Z36" s="9"/>
       <c r="AA36" s="9"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>86</v>
       </c>
@@ -8733,7 +9361,7 @@
         <v>215</v>
       </c>
       <c r="D37" s="7">
-        <v>34.01556</v>
+        <v>34.015560000000001</v>
       </c>
       <c r="E37" s="7">
         <v>-119.361</v>
@@ -8761,7 +9389,7 @@
       <c r="Z37" s="9"/>
       <c r="AA37" s="9"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>216</v>
       </c>
@@ -8772,7 +9400,7 @@
         <v>217</v>
       </c>
       <c r="D38" s="7">
-        <v>33.91835</v>
+        <v>33.918349999999997</v>
       </c>
       <c r="E38" s="7">
         <v>-120.146</v>
@@ -8800,7 +9428,7 @@
       <c r="Z38" s="9"/>
       <c r="AA38" s="9"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>16</v>
       </c>
@@ -8811,7 +9439,7 @@
         <v>218</v>
       </c>
       <c r="D39" s="7">
-        <v>33.91835</v>
+        <v>33.918349999999997</v>
       </c>
       <c r="E39" s="7">
         <v>-120.146</v>
@@ -8839,7 +9467,7 @@
       <c r="Z39" s="9"/>
       <c r="AA39" s="9"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>29</v>
       </c>
@@ -8850,7 +9478,7 @@
         <v>219</v>
       </c>
       <c r="D40" s="7">
-        <v>33.91835</v>
+        <v>33.918349999999997</v>
       </c>
       <c r="E40" s="7">
         <v>-120.146</v>
@@ -8878,7 +9506,7 @@
       <c r="Z40" s="9"/>
       <c r="AA40" s="9"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>146</v>
       </c>
@@ -8889,7 +9517,7 @@
         <v>220</v>
       </c>
       <c r="D41" s="7">
-        <v>34.00516</v>
+        <v>34.005159999999997</v>
       </c>
       <c r="E41" s="7">
         <v>-120.179</v>
@@ -8917,7 +9545,7 @@
       <c r="Z41" s="9"/>
       <c r="AA41" s="9"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>113</v>
       </c>
@@ -8928,7 +9556,7 @@
         <v>221</v>
       </c>
       <c r="D42" s="7">
-        <v>33.47493</v>
+        <v>33.474930000000001</v>
       </c>
       <c r="E42" s="7">
         <v>-119.038</v>
@@ -8956,7 +9584,7 @@
       <c r="Z42" s="9"/>
       <c r="AA42" s="9"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>198</v>
       </c>
@@ -8967,7 +9595,7 @@
         <v>222</v>
       </c>
       <c r="D43" s="7">
-        <v>33.47493</v>
+        <v>33.474930000000001</v>
       </c>
       <c r="E43" s="7">
         <v>-119.038</v>
@@ -8995,7 +9623,7 @@
       <c r="Z43" s="9"/>
       <c r="AA43" s="9"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>123</v>
       </c>
@@ -9006,7 +9634,7 @@
         <v>223</v>
       </c>
       <c r="D44" s="7">
-        <v>33.47493</v>
+        <v>33.474930000000001</v>
       </c>
       <c r="E44" s="7">
         <v>-119.038</v>
@@ -9034,7 +9662,7 @@
       <c r="Z44" s="9"/>
       <c r="AA44" s="9"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>88</v>
       </c>
@@ -9045,10 +9673,10 @@
         <v>224</v>
       </c>
       <c r="D45" s="7">
-        <v>34.01528</v>
+        <v>34.015279999999997</v>
       </c>
       <c r="E45" s="7">
-        <v>-119.362</v>
+        <v>-119.36199999999999</v>
       </c>
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
@@ -9073,7 +9701,7 @@
       <c r="Z45" s="9"/>
       <c r="AA45" s="9"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>148</v>
       </c>
@@ -9084,7 +9712,7 @@
         <v>225</v>
       </c>
       <c r="D46" s="7">
-        <v>34.01583</v>
+        <v>34.015830000000001</v>
       </c>
       <c r="E46" s="7">
         <v>-119.36</v>
@@ -9112,7 +9740,7 @@
       <c r="Z46" s="9"/>
       <c r="AA46" s="9"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>90</v>
       </c>
@@ -9151,7 +9779,7 @@
       <c r="Z47" s="9"/>
       <c r="AA47" s="9"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>93</v>
       </c>
@@ -9190,7 +9818,7 @@
       <c r="Z48" s="9"/>
       <c r="AA48" s="9"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>228</v>
       </c>
@@ -9229,7 +9857,7 @@
       <c r="Z49" s="9"/>
       <c r="AA49" s="9"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>83</v>
       </c>
@@ -9240,13 +9868,13 @@
         <v>231</v>
       </c>
       <c r="D50" s="7">
-        <v>-33.6261</v>
+        <v>-33.626100000000001</v>
       </c>
       <c r="E50" s="7">
         <v>22.10913</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>62</v>
       </c>
@@ -9257,13 +9885,13 @@
         <v>233</v>
       </c>
       <c r="D51" s="7">
-        <v>-33.6261</v>
+        <v>-33.626100000000001</v>
       </c>
       <c r="E51" s="7">
         <v>22.10913</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>81</v>
       </c>
@@ -9274,13 +9902,13 @@
         <v>235</v>
       </c>
       <c r="D52" s="7">
-        <v>-33.6261</v>
+        <v>-33.626100000000001</v>
       </c>
       <c r="E52" s="7">
         <v>22.10913</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>104</v>
       </c>
@@ -9291,13 +9919,13 @@
         <v>236</v>
       </c>
       <c r="D53" s="7">
-        <v>-33.6261</v>
+        <v>-33.626100000000001</v>
       </c>
       <c r="E53" s="7">
         <v>22.10913</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>194</v>
       </c>
@@ -9308,13 +9936,13 @@
         <v>237</v>
       </c>
       <c r="D54" s="7">
-        <v>-33.4484</v>
+        <v>-33.448399999999999</v>
       </c>
       <c r="E54" s="7">
-        <v>25.48108</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>25.481079999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>47</v>
       </c>
@@ -9325,13 +9953,13 @@
         <v>240</v>
       </c>
       <c r="D55" s="7">
-        <v>-33.4484</v>
+        <v>-33.448399999999999</v>
       </c>
       <c r="E55" s="7">
-        <v>25.48108</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>25.481079999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>39</v>
       </c>
@@ -9342,13 +9970,13 @@
         <v>241</v>
       </c>
       <c r="D56" s="7">
-        <v>-33.4484</v>
+        <v>-33.448399999999999</v>
       </c>
       <c r="E56" s="7">
-        <v>25.48108</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>25.481079999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>242</v>
       </c>
@@ -9359,13 +9987,13 @@
         <v>243</v>
       </c>
       <c r="D57" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="E57" s="7">
         <v>18.24061</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>32</v>
       </c>
@@ -9376,13 +10004,13 @@
         <v>246</v>
       </c>
       <c r="D58" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="E58" s="7">
         <v>18.24061</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>67</v>
       </c>
@@ -9393,13 +10021,13 @@
         <v>247</v>
       </c>
       <c r="D59" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="E59" s="7">
         <v>18.24061</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>76</v>
       </c>
@@ -9410,13 +10038,13 @@
         <v>248</v>
       </c>
       <c r="D60" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="E60" s="7">
         <v>18.24061</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>150</v>
       </c>
@@ -9427,13 +10055,13 @@
         <v>249</v>
       </c>
       <c r="D61" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="E61" s="7">
         <v>18.24061</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>65</v>
       </c>
@@ -9444,13 +10072,13 @@
         <v>250</v>
       </c>
       <c r="D62" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="E62" s="7">
         <v>18.24061</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>251</v>
       </c>
@@ -9461,13 +10089,13 @@
         <v>252</v>
       </c>
       <c r="D63" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="E63" s="7">
         <v>18.24061</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>253</v>
       </c>
@@ -9478,13 +10106,13 @@
         <v>254</v>
       </c>
       <c r="D64" s="7">
-        <v>-33.6332</v>
+        <v>-33.633200000000002</v>
       </c>
       <c r="E64" s="7">
         <v>22.21603</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>74</v>
       </c>
@@ -9495,13 +10123,13 @@
         <v>256</v>
       </c>
       <c r="D65" s="7">
-        <v>-33.6332</v>
+        <v>-33.633200000000002</v>
       </c>
       <c r="E65" s="7">
         <v>22.21603</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>79</v>
       </c>
@@ -9512,13 +10140,13 @@
         <v>257</v>
       </c>
       <c r="D66" s="7">
-        <v>-33.6332</v>
+        <v>-33.633200000000002</v>
       </c>
       <c r="E66" s="7">
         <v>22.21603</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>72</v>
       </c>
@@ -9529,13 +10157,13 @@
         <v>258</v>
       </c>
       <c r="D67" s="7">
-        <v>-33.6332</v>
+        <v>-33.633200000000002</v>
       </c>
       <c r="E67" s="7">
         <v>22.21603</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>259</v>
       </c>
@@ -9546,13 +10174,13 @@
         <v>260</v>
       </c>
       <c r="D68" s="7">
-        <v>-31.7569</v>
+        <v>-31.756900000000002</v>
       </c>
       <c r="E68" s="7">
-        <v>18.22694</v>
-      </c>
-    </row>
-    <row r="69">
+        <v>18.226939999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>153</v>
       </c>
@@ -9563,13 +10191,13 @@
         <v>262</v>
       </c>
       <c r="D69" s="7">
-        <v>-31.7569</v>
+        <v>-31.756900000000002</v>
       </c>
       <c r="E69" s="7">
-        <v>18.22694</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>18.226939999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>102</v>
       </c>
@@ -9580,13 +10208,13 @@
         <v>263</v>
       </c>
       <c r="D70" s="7">
-        <v>-31.7569</v>
+        <v>-31.756900000000002</v>
       </c>
       <c r="E70" s="7">
-        <v>18.22694</v>
-      </c>
-    </row>
-    <row r="71">
+        <v>18.226939999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>264</v>
       </c>
@@ -9597,13 +10225,13 @@
         <v>265</v>
       </c>
       <c r="D71" s="7">
-        <v>-31.5267</v>
+        <v>-31.526700000000002</v>
       </c>
       <c r="E71" s="7">
-        <v>18.86556</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>18.865559999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>137</v>
       </c>
@@ -9614,13 +10242,13 @@
         <v>268</v>
       </c>
       <c r="D72" s="7">
-        <v>-31.5267</v>
+        <v>-31.526700000000002</v>
       </c>
       <c r="E72" s="7">
-        <v>18.86556</v>
-      </c>
-    </row>
-    <row r="73">
+        <v>18.865559999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>109</v>
       </c>
@@ -9631,13 +10259,13 @@
         <v>269</v>
       </c>
       <c r="D73" s="7">
-        <v>-31.5267</v>
+        <v>-31.526700000000002</v>
       </c>
       <c r="E73" s="7">
-        <v>18.86556</v>
-      </c>
-    </row>
-    <row r="74">
+        <v>18.865559999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>270</v>
       </c>
@@ -9648,13 +10276,13 @@
         <v>271</v>
       </c>
       <c r="D74" s="7">
-        <v>-31.4658</v>
+        <v>-31.465800000000002</v>
       </c>
       <c r="E74" s="7">
         <v>19.78556</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
         <v>49</v>
       </c>
@@ -9665,13 +10293,13 @@
         <v>273</v>
       </c>
       <c r="D75" s="7">
-        <v>-31.4658</v>
+        <v>-31.465800000000002</v>
       </c>
       <c r="E75" s="7">
         <v>19.78556</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
         <v>128</v>
       </c>
@@ -9682,13 +10310,13 @@
         <v>274</v>
       </c>
       <c r="D76" s="7">
-        <v>-31.4658</v>
+        <v>-31.465800000000002</v>
       </c>
       <c r="E76" s="7">
         <v>19.78556</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
         <v>53</v>
       </c>
@@ -9702,10 +10330,10 @@
         <v>-30.3461</v>
       </c>
       <c r="E77" s="7">
-        <v>17.28306</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>17.283059999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
         <v>277</v>
       </c>
@@ -9719,10 +10347,10 @@
         <v>-30.3461</v>
       </c>
       <c r="E78" s="7">
-        <v>17.28306</v>
-      </c>
-    </row>
-    <row r="79">
+        <v>17.283059999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
         <v>121</v>
       </c>
@@ -9733,13 +10361,13 @@
         <v>279</v>
       </c>
       <c r="D79" s="7">
-        <v>-29.6786</v>
+        <v>-29.678599999999999</v>
       </c>
       <c r="E79" s="7">
-        <v>17.06167</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>17.061669999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
         <v>281</v>
       </c>
@@ -9750,13 +10378,13 @@
         <v>282</v>
       </c>
       <c r="D80" s="7">
-        <v>-29.6786</v>
+        <v>-29.678599999999999</v>
       </c>
       <c r="E80" s="7">
-        <v>17.06167</v>
-      </c>
-    </row>
-    <row r="81">
+        <v>17.061669999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
         <v>283</v>
       </c>
@@ -9770,10 +10398,10 @@
         <v>-33.0608</v>
       </c>
       <c r="E81" s="7">
-        <v>18.04283</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>18.042829999999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
         <v>286</v>
       </c>
@@ -9787,10 +10415,10 @@
         <v>-33.0608</v>
       </c>
       <c r="E82" s="7">
-        <v>18.04283</v>
-      </c>
-    </row>
-    <row r="83">
+        <v>18.042829999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
         <v>288</v>
       </c>
@@ -9801,13 +10429,13 @@
         <v>289</v>
       </c>
       <c r="D83" s="7">
-        <v>-33.6831</v>
+        <v>-33.683100000000003</v>
       </c>
       <c r="E83" s="7">
-        <v>19.59444</v>
-      </c>
-    </row>
-    <row r="84">
+        <v>19.594439999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
         <v>291</v>
       </c>
@@ -9818,13 +10446,13 @@
         <v>292</v>
       </c>
       <c r="D84" s="7">
-        <v>-33.6831</v>
+        <v>-33.683100000000003</v>
       </c>
       <c r="E84" s="7">
-        <v>19.59444</v>
-      </c>
-    </row>
-    <row r="85">
+        <v>19.594439999999999</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
         <v>143</v>
       </c>
@@ -9835,25 +10463,26 @@
         <v>293</v>
       </c>
       <c r="D85" s="7">
-        <v>-33.6831</v>
+        <v>-33.683100000000003</v>
       </c>
       <c r="E85" s="7">
-        <v>19.59444</v>
+        <v>19.594439999999999</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:AB31"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>317</v>
       </c>
@@ -9870,7 +10499,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>16</v>
       </c>
@@ -9881,10 +10510,10 @@
         <v>17</v>
       </c>
       <c r="D2" s="7">
-        <v>-32.7032</v>
+        <v>-32.703200000000002</v>
       </c>
       <c r="E2" s="7">
-        <v>18.2203</v>
+        <v>18.220300000000002</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -9909,7 +10538,7 @@
       <c r="AA2" s="9"/>
       <c r="AB2" s="9"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>93</v>
       </c>
@@ -9920,10 +10549,10 @@
         <v>160</v>
       </c>
       <c r="D3" s="7">
-        <v>35.1264</v>
+        <v>35.126399999999997</v>
       </c>
       <c r="E3" s="7">
-        <v>33.4299</v>
+        <v>33.429900000000004</v>
       </c>
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
@@ -9948,7 +10577,7 @@
       <c r="AA3" s="9"/>
       <c r="AB3" s="9"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>164</v>
       </c>
@@ -9959,10 +10588,10 @@
         <v>165</v>
       </c>
       <c r="D4" s="7">
-        <v>35.1264</v>
+        <v>35.126399999999997</v>
       </c>
       <c r="E4" s="7">
-        <v>33.4299</v>
+        <v>33.429900000000004</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
@@ -9987,7 +10616,7 @@
       <c r="AA4" s="9"/>
       <c r="AB4" s="9"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>140</v>
       </c>
@@ -9998,7 +10627,7 @@
         <v>186</v>
       </c>
       <c r="D5" s="7">
-        <v>27.49364</v>
+        <v>27.493639999999999</v>
       </c>
       <c r="E5" s="7">
         <v>-114.149</v>
@@ -10026,7 +10655,7 @@
       <c r="AA5" s="9"/>
       <c r="AB5" s="9"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>25</v>
       </c>
@@ -10037,7 +10666,7 @@
         <v>187</v>
       </c>
       <c r="D6" s="7">
-        <v>27.45517</v>
+        <v>27.455169999999999</v>
       </c>
       <c r="E6" s="7">
         <v>-114.136</v>
@@ -10065,7 +10694,7 @@
       <c r="AA6" s="9"/>
       <c r="AB6" s="9"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>62</v>
       </c>
@@ -10076,10 +10705,10 @@
         <v>192</v>
       </c>
       <c r="D7" s="7">
-        <v>28.82333</v>
+        <v>28.823329999999999</v>
       </c>
       <c r="E7" s="7">
-        <v>-10.2878</v>
+        <v>-10.287800000000001</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
@@ -10104,7 +10733,7 @@
       <c r="AA7" s="9"/>
       <c r="AB7" s="9"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>81</v>
       </c>
@@ -10115,10 +10744,10 @@
         <v>193</v>
       </c>
       <c r="D8" s="7">
-        <v>28.82333</v>
+        <v>28.823329999999999</v>
       </c>
       <c r="E8" s="7">
-        <v>-10.2878</v>
+        <v>-10.287800000000001</v>
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
@@ -10143,7 +10772,7 @@
       <c r="AA8" s="9"/>
       <c r="AB8" s="9"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>194</v>
       </c>
@@ -10182,7 +10811,7 @@
       <c r="AA9" s="9"/>
       <c r="AB9" s="9"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>198</v>
       </c>
@@ -10221,7 +10850,7 @@
       <c r="AA10" s="9"/>
       <c r="AB10" s="9"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>29</v>
       </c>
@@ -10260,7 +10889,7 @@
       <c r="AA11" s="9"/>
       <c r="AB11" s="9"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>207</v>
       </c>
@@ -10271,13 +10900,13 @@
         <v>294</v>
       </c>
       <c r="D12" s="7">
-        <v>-33.4484</v>
+        <v>-33.448399999999999</v>
       </c>
       <c r="E12" s="7">
-        <v>25.48108</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>25.481079999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>18</v>
       </c>
@@ -10288,13 +10917,13 @@
         <v>296</v>
       </c>
       <c r="D13" s="7">
-        <v>-33.4484</v>
+        <v>-33.448399999999999</v>
       </c>
       <c r="E13" s="7">
-        <v>25.48108</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>25.481079999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>171</v>
       </c>
@@ -10305,13 +10934,13 @@
         <v>297</v>
       </c>
       <c r="D14" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="E14" s="7">
         <v>18.24061</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>128</v>
       </c>
@@ -10322,13 +10951,13 @@
         <v>298</v>
       </c>
       <c r="D15" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="E15" s="7">
         <v>18.24061</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>283</v>
       </c>
@@ -10339,13 +10968,13 @@
         <v>299</v>
       </c>
       <c r="D16" s="7">
-        <v>-32.6861</v>
+        <v>-32.686100000000003</v>
       </c>
       <c r="E16" s="7">
         <v>18.24061</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>107</v>
       </c>
@@ -10356,13 +10985,13 @@
         <v>300</v>
       </c>
       <c r="D17" s="7">
-        <v>-33.6332</v>
+        <v>-33.633200000000002</v>
       </c>
       <c r="E17" s="7">
         <v>22.21603</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>55</v>
       </c>
@@ -10373,13 +11002,13 @@
         <v>301</v>
       </c>
       <c r="D18" s="7">
-        <v>-31.7569</v>
+        <v>-31.756900000000002</v>
       </c>
       <c r="E18" s="7">
-        <v>18.22694</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>18.226939999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>10</v>
       </c>
@@ -10390,13 +11019,13 @@
         <v>302</v>
       </c>
       <c r="D19" s="7">
-        <v>-31.7569</v>
+        <v>-31.756900000000002</v>
       </c>
       <c r="E19" s="7">
-        <v>18.22694</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>18.226939999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>76</v>
       </c>
@@ -10407,13 +11036,13 @@
         <v>303</v>
       </c>
       <c r="D20" s="7">
-        <v>-31.5267</v>
+        <v>-31.526700000000002</v>
       </c>
       <c r="E20" s="7">
-        <v>18.86556</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>18.865559999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>228</v>
       </c>
@@ -10424,13 +11053,13 @@
         <v>304</v>
       </c>
       <c r="D21" s="7">
-        <v>-31.5267</v>
+        <v>-31.526700000000002</v>
       </c>
       <c r="E21" s="7">
-        <v>18.86556</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>18.865559999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>153</v>
       </c>
@@ -10441,13 +11070,13 @@
         <v>305</v>
       </c>
       <c r="D22" s="7">
-        <v>-31.4658</v>
+        <v>-31.465800000000002</v>
       </c>
       <c r="E22" s="7">
         <v>19.78556</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>88</v>
       </c>
@@ -10458,13 +11087,13 @@
         <v>306</v>
       </c>
       <c r="D23" s="7">
-        <v>-31.4658</v>
+        <v>-31.465800000000002</v>
       </c>
       <c r="E23" s="7">
         <v>19.78556</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>201</v>
       </c>
@@ -10478,10 +11107,10 @@
         <v>-30.3461</v>
       </c>
       <c r="E24" s="7">
-        <v>17.28306</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>17.283059999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>146</v>
       </c>
@@ -10495,10 +11124,10 @@
         <v>-30.3461</v>
       </c>
       <c r="E25" s="7">
-        <v>17.28306</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>17.283059999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>119</v>
       </c>
@@ -10512,10 +11141,10 @@
         <v>-30.3461</v>
       </c>
       <c r="E26" s="7">
-        <v>17.28306</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>17.283059999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>310</v>
       </c>
@@ -10526,13 +11155,13 @@
         <v>311</v>
       </c>
       <c r="D27" s="7">
-        <v>-29.6786</v>
+        <v>-29.678599999999999</v>
       </c>
       <c r="E27" s="7">
-        <v>17.06167</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>17.061669999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>135</v>
       </c>
@@ -10543,13 +11172,13 @@
         <v>312</v>
       </c>
       <c r="D28" s="7">
-        <v>-29.6786</v>
+        <v>-29.678599999999999</v>
       </c>
       <c r="E28" s="7">
-        <v>17.06167</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>17.061669999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>123</v>
       </c>
@@ -10563,10 +11192,10 @@
         <v>-33.0608</v>
       </c>
       <c r="E29" s="7">
-        <v>18.04283</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>18.042829999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>34</v>
       </c>
@@ -10577,13 +11206,13 @@
         <v>314</v>
       </c>
       <c r="D30" s="7">
-        <v>-33.6831</v>
+        <v>-33.683100000000003</v>
       </c>
       <c r="E30" s="7">
-        <v>19.59444</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>19.594439999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>113</v>
       </c>
@@ -10594,25 +11223,26 @@
         <v>315</v>
       </c>
       <c r="D31" s="7">
-        <v>-33.6831</v>
+        <v>-33.683100000000003</v>
       </c>
       <c r="E31" s="7">
-        <v>19.59444</v>
+        <v>19.594439999999999</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:E58"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>317</v>
       </c>
@@ -10629,7 +11259,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>29</v>
       </c>
@@ -10640,13 +11270,13 @@
         <v>31</v>
       </c>
       <c r="D2" s="2">
-        <v>-33.0973151</v>
+        <v>-33.097315100000003</v>
       </c>
       <c r="E2" s="2">
-        <v>18.0303847</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
+        <v>18.030384699999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>32</v>
       </c>
@@ -10657,13 +11287,13 @@
         <v>33</v>
       </c>
       <c r="D3" s="2">
-        <v>-33.0973151</v>
+        <v>-33.097315100000003</v>
       </c>
       <c r="E3" s="2">
-        <v>18.0303847</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
+        <v>18.030384699999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>34</v>
       </c>
@@ -10674,13 +11304,13 @@
         <v>35</v>
       </c>
       <c r="D4" s="2">
-        <v>-33.0973151</v>
+        <v>-33.097315100000003</v>
       </c>
       <c r="E4" s="2">
-        <v>18.0303847</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
+        <v>18.030384699999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -10691,13 +11321,13 @@
         <v>38</v>
       </c>
       <c r="D5" s="2">
-        <v>-33.8158702</v>
+        <v>-33.815870199999999</v>
       </c>
       <c r="E5" s="2">
-        <v>18.4728083</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
+        <v>18.472808300000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>39</v>
       </c>
@@ -10708,13 +11338,13 @@
         <v>40</v>
       </c>
       <c r="D6" s="2">
-        <v>-33.8158702</v>
+        <v>-33.815870199999999</v>
       </c>
       <c r="E6" s="2">
-        <v>18.4728083</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
+        <v>18.472808300000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>41</v>
       </c>
@@ -10725,13 +11355,13 @@
         <v>42</v>
       </c>
       <c r="D7" s="2">
-        <v>-33.8158702</v>
+        <v>-33.815870199999999</v>
       </c>
       <c r="E7" s="2">
-        <v>18.4728083</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
+        <v>18.472808300000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>25</v>
       </c>
@@ -10742,13 +11372,13 @@
         <v>44</v>
       </c>
       <c r="D8" s="2">
-        <v>-34.1302817</v>
+        <v>-34.130281699999998</v>
       </c>
       <c r="E8" s="2">
-        <v>18.4490876</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
+        <v>18.449087599999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>45</v>
       </c>
@@ -10759,13 +11389,13 @@
         <v>46</v>
       </c>
       <c r="D9" s="2">
-        <v>-34.1302817</v>
+        <v>-34.130281699999998</v>
       </c>
       <c r="E9" s="2">
-        <v>18.4490876</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
+        <v>18.449087599999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>47</v>
       </c>
@@ -10776,13 +11406,13 @@
         <v>48</v>
       </c>
       <c r="D10" s="2">
-        <v>-34.1302817</v>
+        <v>-34.130281699999998</v>
       </c>
       <c r="E10" s="2">
-        <v>18.4490876</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
+        <v>18.449087599999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>49</v>
       </c>
@@ -10793,13 +11423,13 @@
         <v>51</v>
       </c>
       <c r="D11" s="2">
-        <v>-34.39463</v>
+        <v>-34.394629999999999</v>
       </c>
       <c r="E11" s="2">
-        <v>20.8469878</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
+        <v>20.846987800000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
@@ -10810,13 +11440,13 @@
         <v>52</v>
       </c>
       <c r="D12" s="2">
-        <v>-34.39463</v>
+        <v>-34.394629999999999</v>
       </c>
       <c r="E12" s="2">
-        <v>20.8469878</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
+        <v>20.846987800000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>53</v>
       </c>
@@ -10827,13 +11457,13 @@
         <v>54</v>
       </c>
       <c r="D13" s="2">
-        <v>-34.39463</v>
+        <v>-34.394629999999999</v>
       </c>
       <c r="E13" s="2">
-        <v>20.8469878</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
+        <v>20.846987800000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>55</v>
       </c>
@@ -10844,13 +11474,13 @@
         <v>57</v>
       </c>
       <c r="D14" s="2">
-        <v>-32.2199328</v>
+        <v>-32.219932800000002</v>
       </c>
       <c r="E14" s="2">
         <v>18.4802766</v>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
+    <row r="15" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>58</v>
       </c>
@@ -10861,13 +11491,13 @@
         <v>59</v>
       </c>
       <c r="D15" s="2">
-        <v>-32.2199328</v>
+        <v>-32.219932800000002</v>
       </c>
       <c r="E15" s="2">
         <v>18.4802766</v>
       </c>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
+    <row r="16" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>60</v>
       </c>
@@ -10878,13 +11508,13 @@
         <v>61</v>
       </c>
       <c r="D16" s="2">
-        <v>-32.2199328</v>
+        <v>-32.219932800000002</v>
       </c>
       <c r="E16" s="2">
         <v>18.4802766</v>
       </c>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
+    <row r="17" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>62</v>
       </c>
@@ -10898,10 +11528,10 @@
         <v>-34.831944</v>
       </c>
       <c r="E17" s="2">
-        <v>20.001667</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
+        <v>20.001667000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>65</v>
       </c>
@@ -10915,10 +11545,10 @@
         <v>-34.831944</v>
       </c>
       <c r="E18" s="2">
-        <v>20.001667</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" customHeight="1">
+        <v>20.001667000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>67</v>
       </c>
@@ -10932,10 +11562,10 @@
         <v>-34.831944</v>
       </c>
       <c r="E19" s="2">
-        <v>20.001667</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
+        <v>20.001667000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>69</v>
       </c>
@@ -10946,13 +11576,13 @@
         <v>71</v>
       </c>
       <c r="D20" s="2">
-        <v>-33.3447647</v>
+        <v>-33.344764699999999</v>
       </c>
       <c r="E20" s="2">
-        <v>18.1623146</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
+        <v>18.162314599999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>72</v>
       </c>
@@ -10963,13 +11593,13 @@
         <v>73</v>
       </c>
       <c r="D21" s="2">
-        <v>-33.3447647</v>
+        <v>-33.344764699999999</v>
       </c>
       <c r="E21" s="2">
-        <v>18.1623146</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
+        <v>18.162314599999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>74</v>
       </c>
@@ -10980,13 +11610,13 @@
         <v>75</v>
       </c>
       <c r="D22" s="2">
-        <v>-33.3447647</v>
+        <v>-33.344764699999999</v>
       </c>
       <c r="E22" s="2">
-        <v>18.1623146</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" customHeight="1">
+        <v>18.162314599999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>76</v>
       </c>
@@ -11000,10 +11630,10 @@
         <v>-34.402428</v>
       </c>
       <c r="E23" s="2">
-        <v>19.123211</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25" customHeight="1">
+        <v>19.123211000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>79</v>
       </c>
@@ -11017,10 +11647,10 @@
         <v>-34.402428</v>
       </c>
       <c r="E24" s="2">
-        <v>19.123211</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" customHeight="1">
+        <v>19.123211000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>81</v>
       </c>
@@ -11034,10 +11664,10 @@
         <v>-34.402428</v>
       </c>
       <c r="E25" s="2">
-        <v>19.123211</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25" customHeight="1">
+        <v>19.123211000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>83</v>
       </c>
@@ -11048,13 +11678,13 @@
         <v>85</v>
       </c>
       <c r="D26" s="2">
-        <v>-30.314914</v>
+        <v>-30.314914000000002</v>
       </c>
       <c r="E26" s="2">
-        <v>17.275844</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" customHeight="1">
+        <v>17.275843999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>86</v>
       </c>
@@ -11065,13 +11695,13 @@
         <v>87</v>
       </c>
       <c r="D27" s="2">
-        <v>-30.314914</v>
+        <v>-30.314914000000002</v>
       </c>
       <c r="E27" s="2">
-        <v>17.275844</v>
-      </c>
-    </row>
-    <row r="28" ht="14.25" customHeight="1">
+        <v>17.275843999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>88</v>
       </c>
@@ -11082,13 +11712,13 @@
         <v>89</v>
       </c>
       <c r="D28" s="2">
-        <v>-30.314914</v>
+        <v>-30.314914000000002</v>
       </c>
       <c r="E28" s="2">
-        <v>17.275844</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" customHeight="1">
+        <v>17.275843999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>90</v>
       </c>
@@ -11099,13 +11729,13 @@
         <v>92</v>
       </c>
       <c r="D29" s="2">
-        <v>-34.665278</v>
+        <v>-34.665278000000001</v>
       </c>
       <c r="E29" s="2">
         <v>20.232222</v>
       </c>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
+    <row r="30" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>93</v>
       </c>
@@ -11116,13 +11746,13 @@
         <v>94</v>
       </c>
       <c r="D30" s="2">
-        <v>-34.665278</v>
+        <v>-34.665278000000001</v>
       </c>
       <c r="E30" s="2">
         <v>20.232222</v>
       </c>
     </row>
-    <row r="31" ht="14.25" customHeight="1">
+    <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>95</v>
       </c>
@@ -11133,13 +11763,13 @@
         <v>96</v>
       </c>
       <c r="D31" s="2">
-        <v>-34.665278</v>
+        <v>-34.665278000000001</v>
       </c>
       <c r="E31" s="2">
         <v>20.232222</v>
       </c>
     </row>
-    <row r="32" ht="14.25" customHeight="1">
+    <row r="32" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>97</v>
       </c>
@@ -11150,13 +11780,13 @@
         <v>99</v>
       </c>
       <c r="D32" s="2">
-        <v>-34.3966518</v>
+        <v>-34.396651800000001</v>
       </c>
       <c r="E32" s="2">
         <v>20.8253162</v>
       </c>
     </row>
-    <row r="33" ht="14.25" customHeight="1">
+    <row r="33" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>100</v>
       </c>
@@ -11167,13 +11797,13 @@
         <v>101</v>
       </c>
       <c r="D33" s="2">
-        <v>-34.3966518</v>
+        <v>-34.396651800000001</v>
       </c>
       <c r="E33" s="2">
         <v>20.8253162</v>
       </c>
     </row>
-    <row r="34" ht="14.25" customHeight="1">
+    <row r="34" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>102</v>
       </c>
@@ -11184,13 +11814,13 @@
         <v>103</v>
       </c>
       <c r="D34" s="2">
-        <v>-34.3966518</v>
+        <v>-34.396651800000001</v>
       </c>
       <c r="E34" s="2">
         <v>20.8253162</v>
       </c>
     </row>
-    <row r="35" ht="14.25" customHeight="1">
+    <row r="35" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>104</v>
       </c>
@@ -11201,13 +11831,13 @@
         <v>106</v>
       </c>
       <c r="D35" s="2">
-        <v>-34.624917</v>
+        <v>-34.624917000000003</v>
       </c>
       <c r="E35" s="2">
-        <v>19.336563</v>
-      </c>
-    </row>
-    <row r="36" ht="14.25" customHeight="1">
+        <v>19.336563000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>107</v>
       </c>
@@ -11218,13 +11848,13 @@
         <v>108</v>
       </c>
       <c r="D36" s="2">
-        <v>-34.624917</v>
+        <v>-34.624917000000003</v>
       </c>
       <c r="E36" s="2">
-        <v>19.336563</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" customHeight="1">
+        <v>19.336563000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>109</v>
       </c>
@@ -11235,13 +11865,13 @@
         <v>110</v>
       </c>
       <c r="D37" s="2">
-        <v>-34.624917</v>
+        <v>-34.624917000000003</v>
       </c>
       <c r="E37" s="2">
-        <v>19.336563</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25" customHeight="1">
+        <v>19.336563000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>22</v>
       </c>
@@ -11252,13 +11882,13 @@
         <v>112</v>
       </c>
       <c r="D38" s="2">
-        <v>-32.340981</v>
+        <v>-32.340980999999999</v>
       </c>
       <c r="E38" s="2">
-        <v>18.319755</v>
-      </c>
-    </row>
-    <row r="39" ht="14.25" customHeight="1">
+        <v>18.319755000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>113</v>
       </c>
@@ -11269,13 +11899,13 @@
         <v>114</v>
       </c>
       <c r="D39" s="2">
-        <v>-32.340981</v>
+        <v>-32.340980999999999</v>
       </c>
       <c r="E39" s="2">
-        <v>18.319755</v>
-      </c>
-    </row>
-    <row r="40" ht="14.25" customHeight="1">
+        <v>18.319755000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>115</v>
       </c>
@@ -11286,13 +11916,13 @@
         <v>116</v>
       </c>
       <c r="D40" s="2">
-        <v>-32.340981</v>
+        <v>-32.340980999999999</v>
       </c>
       <c r="E40" s="2">
-        <v>18.319755</v>
-      </c>
-    </row>
-    <row r="41" ht="14.25" customHeight="1">
+        <v>18.319755000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>18</v>
       </c>
@@ -11303,13 +11933,13 @@
         <v>118</v>
       </c>
       <c r="D41" s="2">
-        <v>-33.904219</v>
+        <v>-33.904218999999998</v>
       </c>
       <c r="E41" s="2">
-        <v>18.397974</v>
-      </c>
-    </row>
-    <row r="42" ht="14.25" customHeight="1">
+        <v>18.397974000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>119</v>
       </c>
@@ -11320,13 +11950,13 @@
         <v>120</v>
       </c>
       <c r="D42" s="2">
-        <v>-33.904219</v>
+        <v>-33.904218999999998</v>
       </c>
       <c r="E42" s="2">
-        <v>18.397974</v>
-      </c>
-    </row>
-    <row r="43" ht="14.25" customHeight="1">
+        <v>18.397974000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>121</v>
       </c>
@@ -11337,13 +11967,13 @@
         <v>122</v>
       </c>
       <c r="D43" s="2">
-        <v>-33.904219</v>
+        <v>-33.904218999999998</v>
       </c>
       <c r="E43" s="2">
-        <v>18.397974</v>
-      </c>
-    </row>
-    <row r="44" ht="14.25" customHeight="1">
+        <v>18.397974000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>123</v>
       </c>
@@ -11354,13 +11984,13 @@
         <v>125</v>
       </c>
       <c r="D44" s="2">
-        <v>-33.720556</v>
+        <v>-33.720556000000002</v>
       </c>
       <c r="E44" s="2">
-        <v>18.451389</v>
-      </c>
-    </row>
-    <row r="45" ht="14.25" customHeight="1">
+        <v>18.451388999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>126</v>
       </c>
@@ -11371,13 +12001,13 @@
         <v>127</v>
       </c>
       <c r="D45" s="2">
-        <v>-33.720556</v>
+        <v>-33.720556000000002</v>
       </c>
       <c r="E45" s="2">
-        <v>18.451389</v>
-      </c>
-    </row>
-    <row r="46" ht="14.25" customHeight="1">
+        <v>18.451388999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>128</v>
       </c>
@@ -11388,13 +12018,13 @@
         <v>129</v>
       </c>
       <c r="D46" s="2">
-        <v>-33.720556</v>
+        <v>-33.720556000000002</v>
       </c>
       <c r="E46" s="2">
-        <v>18.451389</v>
-      </c>
-    </row>
-    <row r="47" ht="14.25" customHeight="1">
+        <v>18.451388999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>130</v>
       </c>
@@ -11405,13 +12035,13 @@
         <v>132</v>
       </c>
       <c r="D47" s="2">
-        <v>-34.302167</v>
+        <v>-34.302166999999997</v>
       </c>
       <c r="E47" s="2">
-        <v>20.591117</v>
-      </c>
-    </row>
-    <row r="48" ht="14.25" customHeight="1">
+        <v>20.591117000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>133</v>
       </c>
@@ -11422,13 +12052,13 @@
         <v>134</v>
       </c>
       <c r="D48" s="2">
-        <v>-34.302167</v>
+        <v>-34.302166999999997</v>
       </c>
       <c r="E48" s="2">
-        <v>20.591117</v>
-      </c>
-    </row>
-    <row r="49" ht="14.25" customHeight="1">
+        <v>20.591117000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>135</v>
       </c>
@@ -11439,13 +12069,13 @@
         <v>136</v>
       </c>
       <c r="D49" s="2">
-        <v>-34.302167</v>
+        <v>-34.302166999999997</v>
       </c>
       <c r="E49" s="2">
-        <v>20.591117</v>
-      </c>
-    </row>
-    <row r="50" ht="14.25" customHeight="1">
+        <v>20.591117000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>137</v>
       </c>
@@ -11456,13 +12086,13 @@
         <v>139</v>
       </c>
       <c r="D50" s="2">
-        <v>-33.85833</v>
+        <v>-33.858330000000002</v>
       </c>
       <c r="E50" s="2">
-        <v>18.489444</v>
-      </c>
-    </row>
-    <row r="51" ht="14.25" customHeight="1">
+        <v>18.489443999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>140</v>
       </c>
@@ -11473,13 +12103,13 @@
         <v>141</v>
       </c>
       <c r="D51" s="2">
-        <v>-33.85833</v>
+        <v>-33.858330000000002</v>
       </c>
       <c r="E51" s="2">
-        <v>18.489444</v>
-      </c>
-    </row>
-    <row r="52" ht="14.25" customHeight="1">
+        <v>18.489443999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>10</v>
       </c>
@@ -11490,13 +12120,13 @@
         <v>142</v>
       </c>
       <c r="D52" s="2">
-        <v>-33.85833</v>
+        <v>-33.858330000000002</v>
       </c>
       <c r="E52" s="2">
-        <v>18.489444</v>
-      </c>
-    </row>
-    <row r="53" ht="14.25" customHeight="1">
+        <v>18.489443999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>143</v>
       </c>
@@ -11507,13 +12137,13 @@
         <v>145</v>
       </c>
       <c r="D53" s="2">
-        <v>-33.7243466</v>
+        <v>-33.724346599999997</v>
       </c>
       <c r="E53" s="2">
-        <v>18.4429942</v>
-      </c>
-    </row>
-    <row r="54" ht="14.25" customHeight="1">
+        <v>18.442994200000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>146</v>
       </c>
@@ -11524,13 +12154,13 @@
         <v>147</v>
       </c>
       <c r="D54" s="2">
-        <v>-33.7243466</v>
+        <v>-33.724346599999997</v>
       </c>
       <c r="E54" s="2">
-        <v>18.4429942</v>
-      </c>
-    </row>
-    <row r="55" ht="14.25" customHeight="1">
+        <v>18.442994200000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>148</v>
       </c>
@@ -11541,13 +12171,13 @@
         <v>149</v>
       </c>
       <c r="D55" s="5">
-        <v>-33.7243466</v>
+        <v>-33.724346599999997</v>
       </c>
       <c r="E55" s="5">
-        <v>18.4429942</v>
-      </c>
-    </row>
-    <row r="56" ht="14.25" customHeight="1">
+        <v>18.442994200000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>150</v>
       </c>
@@ -11558,13 +12188,13 @@
         <v>152</v>
       </c>
       <c r="D56" s="2">
-        <v>-33.5909892</v>
+        <v>-33.590989200000003</v>
       </c>
       <c r="E56" s="2">
-        <v>18.3621042</v>
-      </c>
-    </row>
-    <row r="57" ht="14.25" customHeight="1">
+        <v>18.362104200000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>153</v>
       </c>
@@ -11575,13 +12205,13 @@
         <v>154</v>
       </c>
       <c r="D57" s="2">
-        <v>-33.5909892</v>
+        <v>-33.590989200000003</v>
       </c>
       <c r="E57" s="2">
-        <v>18.3621042</v>
-      </c>
-    </row>
-    <row r="58" ht="14.25" customHeight="1">
+        <v>18.362104200000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>16</v>
       </c>
@@ -11592,30 +12222,31 @@
         <v>155</v>
       </c>
       <c r="D58" s="2">
-        <v>-33.5909892</v>
+        <v>-33.590989200000003</v>
       </c>
       <c r="E58" s="2">
-        <v>18.3621042</v>
+        <v>18.362104200000001</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -11623,7 +12254,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>238</v>
       </c>
@@ -11631,7 +12262,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>232</v>
       </c>
@@ -11639,7 +12270,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>244</v>
       </c>
@@ -11647,7 +12278,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>266</v>
       </c>
@@ -11656,6 +12287,6 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>